--- a/examples/watts_exec_GCMR_A_E5_enr_15p_5y_fleet_output.xlsx
+++ b/examples/watts_exec_GCMR_A_E5_enr_15p_5y_fleet_output.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,25 +702,25 @@
         <v>101199731</v>
       </c>
       <c r="D8" t="n">
-        <v>40994499</v>
+        <v>46936754</v>
       </c>
       <c r="E8" t="n">
         <v>16313059</v>
       </c>
       <c r="F8" t="n">
-        <v>10215680</v>
+        <v>10259642</v>
       </c>
       <c r="G8" t="n">
         <v>148</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="I8" t="n">
         <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1382,25 +1382,25 @@
         <v>40711806</v>
       </c>
       <c r="D28" t="n">
-        <v>8981691</v>
+        <v>14296881</v>
       </c>
       <c r="E28" t="n">
         <v>4410131</v>
       </c>
       <c r="F28" t="n">
-        <v>1084867</v>
+        <v>1595668</v>
       </c>
       <c r="G28" t="n">
         <v>59</v>
       </c>
       <c r="H28" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
         <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2198,25 +2198,25 @@
         <v>9944133</v>
       </c>
       <c r="D52" t="n">
-        <v>1757193</v>
+        <v>7072383</v>
       </c>
       <c r="E52" t="n">
         <v>1858540</v>
       </c>
       <c r="F52" t="n">
-        <v>328416</v>
+        <v>1321815</v>
       </c>
       <c r="G52" t="n">
         <v>14</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I52" t="n">
         <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2266,19 +2266,19 @@
         <v>19351082</v>
       </c>
       <c r="D54" t="n">
-        <v>13135650</v>
+        <v>13762714</v>
       </c>
       <c r="E54" t="n">
         <v>14067156</v>
       </c>
       <c r="F54" t="n">
-        <v>9998382</v>
+        <v>10004725</v>
       </c>
       <c r="G54" t="n">
         <v>28</v>
       </c>
       <c r="H54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" t="n">
         <v>20</v>
@@ -2368,19 +2368,19 @@
         <v>1173168</v>
       </c>
       <c r="D57" t="n">
-        <v>207306</v>
+        <v>834371</v>
       </c>
       <c r="E57" t="n">
         <v>265577</v>
       </c>
       <c r="F57" t="n">
-        <v>46929</v>
+        <v>188881</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -2810,19 +2810,19 @@
         <v>8203844</v>
       </c>
       <c r="D70" t="n">
-        <v>3985325</v>
+        <v>4107110</v>
       </c>
       <c r="E70" t="n">
         <v>1207976</v>
       </c>
       <c r="F70" t="n">
-        <v>642794</v>
+        <v>592168</v>
       </c>
       <c r="G70" t="n">
         <v>12</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -2844,13 +2844,13 @@
         <v>2402935</v>
       </c>
       <c r="D71" t="n">
-        <v>827020</v>
+        <v>1021302</v>
       </c>
       <c r="E71" t="n">
         <v>518545</v>
       </c>
       <c r="F71" t="n">
-        <v>328360</v>
+        <v>330147</v>
       </c>
       <c r="G71" t="n">
         <v>3</v>
@@ -2878,13 +2878,13 @@
         <v>841875</v>
       </c>
       <c r="D72" t="n">
-        <v>308542</v>
+        <v>236045</v>
       </c>
       <c r="E72" t="n">
         <v>554549</v>
       </c>
       <c r="F72" t="n">
-        <v>204327</v>
+        <v>136476</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -3116,13 +3116,13 @@
         <v>2564406</v>
       </c>
       <c r="D79" t="n">
-        <v>1079347</v>
+        <v>1184012</v>
       </c>
       <c r="E79" t="n">
         <v>324417</v>
       </c>
       <c r="F79" t="n">
-        <v>192935</v>
+        <v>192722</v>
       </c>
       <c r="G79" t="n">
         <v>3</v>
@@ -3150,13 +3150,13 @@
         <v>2564406</v>
       </c>
       <c r="D80" t="n">
-        <v>1079347</v>
+        <v>1184012</v>
       </c>
       <c r="E80" t="n">
         <v>324417</v>
       </c>
       <c r="F80" t="n">
-        <v>192935</v>
+        <v>192722</v>
       </c>
       <c r="G80" t="n">
         <v>3</v>
@@ -3181,28 +3181,28 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6351570</v>
+        <v>8465404</v>
       </c>
       <c r="D81" t="n">
-        <v>2856290</v>
+        <v>4784421</v>
       </c>
       <c r="E81" t="n">
-        <v>713262</v>
+        <v>795117</v>
       </c>
       <c r="F81" t="n">
-        <v>370350</v>
+        <v>494426</v>
       </c>
       <c r="G81" t="n">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="H81" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="I81" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
@@ -3215,28 +3215,28 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1004008</v>
+        <v>2852574</v>
       </c>
       <c r="D82" t="n">
-        <v>1004008</v>
+        <v>2852574</v>
       </c>
       <c r="E82" t="n">
-        <v>150518</v>
+        <v>341169</v>
       </c>
       <c r="F82" t="n">
-        <v>150518</v>
+        <v>341169</v>
       </c>
       <c r="G82" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="H82" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6596</v>
+        <v>1855161</v>
       </c>
       <c r="D83" t="n">
-        <v>6596</v>
+        <v>1855161</v>
       </c>
       <c r="E83" t="n">
-        <v>1142</v>
+        <v>321375</v>
       </c>
       <c r="F83" t="n">
-        <v>1142</v>
+        <v>321375</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -3351,22 +3351,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>5162438</v>
+        <v>5427706</v>
       </c>
       <c r="D86" t="n">
-        <v>1775223</v>
+        <v>1846946</v>
       </c>
       <c r="E86" t="n">
-        <v>674160</v>
+        <v>691087</v>
       </c>
       <c r="F86" t="n">
-        <v>318790</v>
+        <v>321111</v>
       </c>
       <c r="G86" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H86" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I86" t="n">
         <v>13</v>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Annualized Core Barrel Replacements</t>
+          <t xml:space="preserve">            Annualized Inner Vessel Structure Replacements</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -3479,514 +3479,434 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">            Annualized Misc. Replacements</t>
+          <t xml:space="preserve">            Annualized Moderator Booster Replacements</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2392327</v>
+        <v>812479</v>
       </c>
       <c r="D90" t="n">
-        <v>1070965</v>
+        <v>143570</v>
       </c>
       <c r="E90" t="n">
-        <v>491781</v>
+        <v>130362</v>
       </c>
       <c r="F90" t="n">
-        <v>309544</v>
+        <v>23035</v>
       </c>
       <c r="G90" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>78</v>
+        <v>759</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Annualized Decommissioning Cost</t>
+          <t xml:space="preserve">            Annualized Plant Maintenance (Misc.)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>184996</v>
+        <v>1845115</v>
       </c>
       <c r="D91" t="n">
-        <v>77030</v>
+        <v>999118</v>
       </c>
       <c r="E91" t="n">
-        <v>23716</v>
+        <v>492309</v>
       </c>
       <c r="F91" t="n">
-        <v>14107</v>
+        <v>313032</v>
       </c>
       <c r="G91" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>80</v>
+        <v>759.1</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Annualized Fuel Cost</t>
+          <t xml:space="preserve">                  Annualized Building and Structural Maintenance (Accounts 212–215)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4130644</v>
+        <v>396991</v>
       </c>
       <c r="D92" t="n">
-        <v>1958052</v>
+        <v>91889</v>
       </c>
       <c r="E92" t="n">
-        <v>450247</v>
+        <v>191201</v>
       </c>
       <c r="F92" t="n">
-        <v>283975</v>
+        <v>34215</v>
       </c>
       <c r="G92" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="H92" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
+        <v>759.2</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Main Heat Transport System Maintenance (Accounts 222.1–222.3 and 222.6)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>69073</v>
+      </c>
+      <c r="D93" t="n">
+        <v>12205</v>
+      </c>
+      <c r="E93" t="n">
+        <v>7229</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1277</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>759.3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Safety System Maintenance (Account 223)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>75563</v>
+      </c>
+      <c r="D94" t="n">
+        <v>13352</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8213</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1451</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>759.4</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Reactor Plant Equipment Maintenance (Accounts 221.11, 226, and 228)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>99960</v>
+      </c>
+      <c r="D95" t="n">
+        <v>25708</v>
+      </c>
+      <c r="E95" t="n">
+        <v>20966</v>
+      </c>
+      <c r="F95" t="n">
+        <v>5407</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>759.5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Reactor I&amp;C Maintenance (Account 227)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>298324</v>
+      </c>
+      <c r="D96" t="n">
+        <v>212171</v>
+      </c>
+      <c r="E96" t="n">
+        <v>55756</v>
+      </c>
+      <c r="F96" t="n">
+        <v>39654</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5</v>
+      </c>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>759.6</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Energy Conversion System Maintenance (Account 23)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>580532</v>
+      </c>
+      <c r="D97" t="n">
+        <v>412881</v>
+      </c>
+      <c r="E97" t="n">
+        <v>422014</v>
+      </c>
+      <c r="F97" t="n">
+        <v>300141</v>
+      </c>
+      <c r="G97" t="n">
+        <v>11</v>
+      </c>
+      <c r="H97" t="n">
+        <v>8</v>
+      </c>
+      <c r="I97" t="n">
+        <v>8</v>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>759.7</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                  Annualized Electrical Equipment Maintenance (Account 24)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>324669</v>
+      </c>
+      <c r="D98" t="n">
+        <v>230908</v>
+      </c>
+      <c r="E98" t="n">
+        <v>95394</v>
+      </c>
+      <c r="F98" t="n">
+        <v>67845</v>
+      </c>
+      <c r="G98" t="n">
+        <v>6</v>
+      </c>
+      <c r="H98" t="n">
+        <v>4</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>78</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Annualized Decommissioning Cost</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>184996</v>
+      </c>
+      <c r="D99" t="n">
+        <v>84871</v>
+      </c>
+      <c r="E99" t="n">
+        <v>23716</v>
+      </c>
+      <c r="F99" t="n">
+        <v>14165</v>
+      </c>
+      <c r="G99" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>80</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Annualized Fuel Cost</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4130644</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1958052</v>
+      </c>
+      <c r="E100" t="n">
+        <v>450247</v>
+      </c>
+      <c r="F100" t="n">
+        <v>283975</v>
+      </c>
+      <c r="G100" t="n">
+        <v>80</v>
+      </c>
+      <c r="H100" t="n">
+        <v>38</v>
+      </c>
+      <c r="I100" t="n">
+        <v>8</v>
+      </c>
+      <c r="J100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
         <v>82</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t xml:space="preserve">      Additional Nuclear Fuel</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="C101" t="n">
         <v>4130644</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D101" t="n">
         <v>1958052</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E101" t="n">
         <v>450247</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F101" t="n">
         <v>283975</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G101" t="n">
         <v>80</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H101" t="n">
         <v>38</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I101" t="n">
         <v>8</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J101" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Overnight Capital Cost</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>148576489</v>
-      </c>
-      <c r="D94" t="n">
-        <v>62535205</v>
-      </c>
-      <c r="E94" t="n">
-        <v>18796068</v>
-      </c>
-      <c r="F94" t="n">
-        <v>11178309</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>OCC per kW</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Overnight Capital Cost per kW</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>24762</v>
-      </c>
-      <c r="D95" t="n">
-        <v>10422</v>
-      </c>
-      <c r="E95" t="n">
-        <v>3132</v>
-      </c>
-      <c r="F95" t="n">
-        <v>1863</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>OCC excl. fuel</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Overnight Capital Cost Excluding Fuel</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>131694659</v>
-      </c>
-      <c r="D96" t="n">
-        <v>54532699</v>
-      </c>
-      <c r="E96" t="n">
-        <v>18774399</v>
-      </c>
-      <c r="F96" t="n">
-        <v>11260101</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>OCC excl. fuel per kW</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Overnight Capital Cost Excluding Fuel per kW</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>21949</v>
-      </c>
-      <c r="D97" t="n">
-        <v>9088</v>
-      </c>
-      <c r="E97" t="n">
-        <v>3129</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1876</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>TCI</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Total Capital Investment</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>151140896</v>
-      </c>
-      <c r="D98" t="n">
-        <v>63614553</v>
-      </c>
-      <c r="E98" t="n">
-        <v>19120486</v>
-      </c>
-      <c r="F98" t="n">
-        <v>11371245</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>TCI per kW</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Total Capital Investment per kW</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>25190</v>
-      </c>
-      <c r="D99" t="n">
-        <v>10602</v>
-      </c>
-      <c r="E99" t="n">
-        <v>3186</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1895</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Annualized Cost</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>10482214</v>
-      </c>
-      <c r="D100" t="n">
-        <v>4814343</v>
-      </c>
-      <c r="E100" t="n">
-        <v>877204</v>
-      </c>
-      <c r="F100" t="n">
-        <v>478703</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>AC per MWh</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Annualized Cost per MWh</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>204</v>
-      </c>
-      <c r="D101" t="n">
-        <v>93</v>
-      </c>
-      <c r="E101" t="n">
-        <v>17</v>
-      </c>
-      <c r="F101" t="n">
-        <v>9</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LCOE</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Levelized Cost Of Energy ($/MWh)</t>
+          <t>Overnight Capital Cost</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>425</v>
+        <v>148576489</v>
       </c>
       <c r="D102" t="n">
-        <v>187</v>
+        <v>68599244</v>
       </c>
       <c r="E102" t="n">
-        <v>40</v>
+        <v>18796068</v>
       </c>
       <c r="F102" t="n">
-        <v>23</v>
+        <v>11165954</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4012,42 +3932,394 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>OCC per kW</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Overnight Capital Cost per kW</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>24762</v>
+      </c>
+      <c r="D103" t="n">
+        <v>11433</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3132</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>OCC excl. fuel</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Overnight Capital Cost Excluding Fuel</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>131694659</v>
+      </c>
+      <c r="D104" t="n">
+        <v>60596739</v>
+      </c>
+      <c r="E104" t="n">
+        <v>18774399</v>
+      </c>
+      <c r="F104" t="n">
+        <v>11245496</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>OCC excl. fuel per kW</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Overnight Capital Cost Excluding Fuel per kW</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>21949</v>
+      </c>
+      <c r="D105" t="n">
+        <v>10099</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3129</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1874</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TCI</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Total Capital Investment</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>151140896</v>
+      </c>
+      <c r="D106" t="n">
+        <v>69783257</v>
+      </c>
+      <c r="E106" t="n">
+        <v>19120486</v>
+      </c>
+      <c r="F106" t="n">
+        <v>11358676</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TCI per kW</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Total Capital Investment per kW</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>25190</v>
+      </c>
+      <c r="D107" t="n">
+        <v>11630</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3186</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1893</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Annualized Cost</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>12596048</v>
+      </c>
+      <c r="D108" t="n">
+        <v>6742473</v>
+      </c>
+      <c r="E108" t="n">
+        <v>908498</v>
+      </c>
+      <c r="F108" t="n">
+        <v>553197</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>AC per MWh</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Annualized Cost per MWh</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>245</v>
+      </c>
+      <c r="D109" t="n">
+        <v>131</v>
+      </c>
+      <c r="E109" t="n">
+        <v>17</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>LCOE</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Levelized Cost Of Energy ($/MWh)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>467</v>
+      </c>
+      <c r="D110" t="n">
+        <v>233</v>
+      </c>
+      <c r="E110" t="n">
+        <v>41</v>
+      </c>
+      <c r="F110" t="n">
+        <v>24</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>LCOH</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>Levelized Cost Of Heat ($/MWth)</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>149</v>
-      </c>
-      <c r="D103" t="n">
-        <v>65</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="C111" t="n">
+        <v>165</v>
+      </c>
+      <c r="D111" t="n">
+        <v>83</v>
+      </c>
+      <c r="E111" t="n">
         <v>14</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F111" t="n">
         <v>8</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4064,7 +4336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4218,13 +4490,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11374009577</v>
+        <v>12874920995</v>
       </c>
       <c r="D8" t="n">
-        <v>3543339975</v>
+        <v>3607357689</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -4237,13 +4509,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7101439783</v>
+        <v>8602351201</v>
       </c>
       <c r="D9" t="n">
-        <v>3552514715</v>
+        <v>3615704429</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -4389,13 +4661,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7056998688</v>
+        <v>8557910106</v>
       </c>
       <c r="D17" t="n">
-        <v>3554168317</v>
+        <v>3617356132</v>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -4574,13 +4846,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51622055</v>
+        <v>1552533473</v>
       </c>
       <c r="D27" t="n">
-        <v>37432502</v>
+        <v>513295585</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -5315,13 +5587,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5687004788</v>
+        <v>6437460497</v>
       </c>
       <c r="D66" t="n">
-        <v>1771669987</v>
+        <v>1803678844</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -5372,10 +5644,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>928819617</v>
+        <v>1050271949</v>
       </c>
       <c r="D69" t="n">
-        <v>286668416</v>
+        <v>291855755</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -5391,10 +5663,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>928819617</v>
+        <v>1050271949</v>
       </c>
       <c r="D70" t="n">
-        <v>286668416</v>
+        <v>291855755</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -5410,13 +5682,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2657716267</v>
+        <v>2792915906</v>
       </c>
       <c r="D71" t="n">
-        <v>594860354</v>
+        <v>596298297</v>
       </c>
       <c r="E71" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72">
@@ -5429,13 +5701,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1581543154</v>
+        <v>1617630869</v>
       </c>
       <c r="D72" t="n">
-        <v>577416438</v>
+        <v>576479426</v>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="73">
@@ -5448,10 +5720,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>596503</v>
+        <v>33553320</v>
       </c>
       <c r="D73" t="n">
-        <v>215889</v>
+        <v>12143762</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -5543,10 +5815,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>28886632</v>
+        <v>29545769</v>
       </c>
       <c r="D78" t="n">
-        <v>10546418</v>
+        <v>10529304</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -5562,10 +5834,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>108324873</v>
+        <v>110796634</v>
       </c>
       <c r="D79" t="n">
-        <v>39549071</v>
+        <v>39484892</v>
       </c>
       <c r="E79" t="n">
         <v>2</v>
@@ -5581,13 +5853,13 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1076173112</v>
+        <v>1175285036</v>
       </c>
       <c r="D80" t="n">
-        <v>85147942</v>
+        <v>91592255</v>
       </c>
       <c r="E80" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -5600,10 +5872,10 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>56870047</v>
+        <v>64374604</v>
       </c>
       <c r="D81" t="n">
-        <v>17716699</v>
+        <v>18036788</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -5638,10 +5910,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>113740095</v>
+        <v>128749209</v>
       </c>
       <c r="D83" t="n">
-        <v>35433399</v>
+        <v>36073576</v>
       </c>
       <c r="E83" t="n">
         <v>2</v>
@@ -5676,10 +5948,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>17653335</v>
+        <v>18779019</v>
       </c>
       <c r="D85" t="n">
-        <v>2654189</v>
+        <v>2702026</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -5695,13 +5967,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>191271332</v>
+        <v>255622764</v>
       </c>
       <c r="D86" t="n">
-        <v>12085120</v>
+        <v>34726404</v>
       </c>
       <c r="E86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
@@ -5763,260 +6035,279 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>747.3</v>
+        <v>747.24</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  Annualized Helium Replenishment</t>
+          <t xml:space="preserve">                        Used Fuel Storage Additional Overpacks</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3678182</v>
+        <v>64351431</v>
       </c>
       <c r="D90" t="n">
-        <v>553400</v>
+        <v>32692560</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>747.4</v>
+        <v>747.3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  Annualized Other Supplies and Utilities</t>
+          <t xml:space="preserve">                  Annualized Helium Replenishment</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>56870047</v>
+        <v>3648726</v>
       </c>
       <c r="D91" t="n">
-        <v>17716699</v>
+        <v>619276</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>747.5</v>
+        <v>747.4</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">                  Servicing Vehicle O&amp;M</t>
+          <t xml:space="preserve">                  Annualized Other Supplies and Utilities</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>359615996</v>
+        <v>64374604</v>
       </c>
       <c r="D92" t="n">
-        <v>42483257</v>
+        <v>18036788</v>
       </c>
       <c r="E92" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>747.51</v>
+        <v>747.5</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        Reactor Transport Vehicles O&amp;M</t>
+          <t xml:space="preserve">                  Servicing Vehicle O&amp;M</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>98946301</v>
+        <v>363262033</v>
       </c>
       <c r="D93" t="n">
-        <v>22383855</v>
+        <v>45482367</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>747.52</v>
+        <v>747.51</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        Helium Transport Trucks O&amp;M</t>
+          <t xml:space="preserve">                        Reactor Transport Vehicles O&amp;M</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>109979625</v>
+        <v>99625535</v>
       </c>
       <c r="D94" t="n">
-        <v>26823335</v>
+        <v>22977516</v>
       </c>
       <c r="E94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>747.53</v>
+        <v>747.52</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">                        Water Tanker Trucks O&amp;M</t>
+          <t xml:space="preserve">                        Helium Transport Trucks O&amp;M</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>101531620</v>
+        <v>113578644</v>
       </c>
       <c r="D95" t="n">
-        <v>23415580</v>
+        <v>26650526</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
+        <v>747.53</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                        Water Tanker Trucks O&amp;M</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>101849860</v>
+      </c>
+      <c r="D96" t="n">
+        <v>22068616</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
         <v>747.54</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t xml:space="preserve">                        Maintenance Trucks O&amp;M</t>
         </is>
       </c>
-      <c r="C96" t="n">
-        <v>49158448</v>
-      </c>
-      <c r="D96" t="n">
-        <v>11919618</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>OCC</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Overnight Capital Cost</t>
-        </is>
-      </c>
       <c r="C97" t="n">
-        <v>17217569320</v>
+        <v>48207992</v>
       </c>
       <c r="D97" t="n">
-        <v>5313984800</v>
+        <v>10223776</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OCC per reactor</t>
+          <t>OCC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Overnight Capital Cost per Operating Reactor</t>
+          <t>Overnight Capital Cost</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17695343</v>
+        <v>19468936447</v>
       </c>
       <c r="D98" t="n">
-        <v>5461443</v>
+        <v>5410142732</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TCI</t>
+          <t>OCC per reactor</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Total Capital Investment</t>
+          <t>Overnight Capital Cost per Operating Reactor</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>18146388937</v>
+        <v>20009184</v>
       </c>
       <c r="D99" t="n">
-        <v>5600653216</v>
+        <v>5560270</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TCI per reactor</t>
+          <t>TCI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Total Capital Investment per Operating Reactor</t>
+          <t>Total Capital Investment</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>18649937</v>
+        <v>20519208397</v>
       </c>
       <c r="D100" t="n">
-        <v>5756067</v>
+        <v>5701998488</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Annual Cost</t>
+          <t>TCI per reactor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Annual Servicing Campus Cost</t>
+          <t>Total Capital Investment per Operating Reactor</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2657716267</v>
+        <v>21088600</v>
       </c>
       <c r="D101" t="n">
-        <v>594860354</v>
+        <v>5860224</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Annual Cost per reactor</t>
+          <t>Annual Cost</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Annual Servicing Campus Cost per Operating Reactor</t>
+          <t>Annual Servicing Campus Cost</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2731465</v>
+        <v>2792915906</v>
       </c>
       <c r="D102" t="n">
-        <v>611367</v>
+        <v>596298297</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Annual Cost per reactor</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Annual Servicing Campus Cost per Operating Reactor</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2870417</v>
+      </c>
+      <c r="D103" t="n">
+        <v>612845</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>LCOE</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>Servicing Campus Contribution to Fleet LCOE ($/MWh)</t>
         </is>
       </c>
-      <c r="C103" t="n">
-        <v>78</v>
-      </c>
-      <c r="D103" t="n">
+      <c r="C104" t="n">
+        <v>84</v>
+      </c>
+      <c r="D104" t="n">
         <v>15</v>
       </c>
     </row>
@@ -7566,10 +7857,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40994499952</v>
+        <v>46936754617</v>
       </c>
       <c r="E3" t="n">
-        <v>10215680956</v>
+        <v>10259642873</v>
       </c>
       <c r="F3" t="n">
         <v>268439482</v>
@@ -7578,16 +7869,16 @@
         <v>26059378</v>
       </c>
       <c r="H3" t="n">
-        <v>11374009577</v>
+        <v>12874920995</v>
       </c>
       <c r="I3" t="n">
-        <v>3543339975</v>
+        <v>3607357690</v>
       </c>
       <c r="J3" t="n">
-        <v>52636949011</v>
+        <v>60080115094</v>
       </c>
       <c r="K3" t="n">
-        <v>10844346671</v>
+        <v>11000057891</v>
       </c>
     </row>
     <row r="4">
@@ -7605,10 +7896,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3985325220</v>
+        <v>4107110030</v>
       </c>
       <c r="E4" t="n">
-        <v>642794067</v>
+        <v>592168902</v>
       </c>
       <c r="F4" t="n">
         <v>134219741</v>
@@ -7617,16 +7908,16 @@
         <v>13029689</v>
       </c>
       <c r="H4" t="n">
-        <v>5687004789</v>
+        <v>6437460498</v>
       </c>
       <c r="I4" t="n">
-        <v>1771669988</v>
+        <v>1803678845</v>
       </c>
       <c r="J4" t="n">
-        <v>9806549750</v>
+        <v>10678790269</v>
       </c>
       <c r="K4" t="n">
-        <v>1819727876</v>
+        <v>1853007175</v>
       </c>
     </row>
     <row r="5">
@@ -7683,10 +7974,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1079347800</v>
+        <v>1184012166</v>
       </c>
       <c r="E6" t="n">
-        <v>192935860</v>
+        <v>192722610</v>
       </c>
       <c r="F6" t="n">
         <v>29853207</v>
@@ -7695,16 +7986,16 @@
         <v>2139796</v>
       </c>
       <c r="H6" t="n">
-        <v>928819617</v>
+        <v>1050271950</v>
       </c>
       <c r="I6" t="n">
-        <v>286668416</v>
+        <v>291855755</v>
       </c>
       <c r="J6" t="n">
-        <v>2038020624</v>
+        <v>2264137323</v>
       </c>
       <c r="K6" t="n">
-        <v>345290323</v>
+        <v>354153013</v>
       </c>
     </row>
     <row r="7">
@@ -7722,10 +8013,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2856290829</v>
+        <v>4784421006</v>
       </c>
       <c r="E7" t="n">
-        <v>370350636</v>
+        <v>494426899</v>
       </c>
       <c r="F7" t="n">
         <v>46536920</v>
@@ -7734,16 +8025,16 @@
         <v>4919974</v>
       </c>
       <c r="H7" t="n">
-        <v>2657716267</v>
+        <v>2792915906</v>
       </c>
       <c r="I7" t="n">
-        <v>594860354</v>
+        <v>596298298</v>
       </c>
       <c r="J7" t="n">
-        <v>5560544016</v>
+        <v>7623873832</v>
       </c>
       <c r="K7" t="n">
-        <v>681196237</v>
+        <v>732303005</v>
       </c>
     </row>
     <row r="8">
@@ -7802,10 +8093,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62535205509</v>
+        <v>68599244983</v>
       </c>
       <c r="E9" t="n">
-        <v>11178309377</v>
+        <v>11165954136</v>
       </c>
       <c r="F9" t="n">
         <v>553390192</v>
@@ -7814,16 +8105,16 @@
         <v>39665493</v>
       </c>
       <c r="H9" t="n">
-        <v>17217569321</v>
+        <v>19468936448</v>
       </c>
       <c r="I9" t="n">
-        <v>5313984800</v>
+        <v>5410142733</v>
       </c>
       <c r="J9" t="n">
-        <v>80306165022</v>
+        <v>88621571624</v>
       </c>
       <c r="K9" t="n">
-        <v>12373518350</v>
+        <v>12544551074</v>
       </c>
     </row>
     <row r="10">
@@ -7843,10 +8134,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62535206</v>
+        <v>68599245</v>
       </c>
       <c r="E10" t="n">
-        <v>11178309</v>
+        <v>11165954</v>
       </c>
       <c r="F10" t="n">
         <v>553390</v>
@@ -7855,16 +8146,16 @@
         <v>39665</v>
       </c>
       <c r="H10" t="n">
-        <v>17217569</v>
+        <v>19468936</v>
       </c>
       <c r="I10" t="n">
-        <v>5313985</v>
+        <v>5410143</v>
       </c>
       <c r="J10" t="n">
-        <v>80306165</v>
+        <v>88621572</v>
       </c>
       <c r="K10" t="n">
-        <v>12373518</v>
+        <v>12544551</v>
       </c>
     </row>
     <row r="11">
@@ -7884,10 +8175,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63614553308</v>
+        <v>69783257149</v>
       </c>
       <c r="E11" t="n">
-        <v>11371245237</v>
+        <v>11358676746</v>
       </c>
       <c r="F11" t="n">
         <v>583243400</v>
@@ -7896,16 +8187,16 @@
         <v>41805289</v>
       </c>
       <c r="H11" t="n">
-        <v>18146388938</v>
+        <v>20519208398</v>
       </c>
       <c r="I11" t="n">
-        <v>5600653216</v>
+        <v>5701998488</v>
       </c>
       <c r="J11" t="n">
-        <v>82344185646</v>
+        <v>90885708947</v>
       </c>
       <c r="K11" t="n">
-        <v>12671826248</v>
+        <v>12852816419</v>
       </c>
     </row>
     <row r="12">
@@ -7925,10 +8216,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>63614553</v>
+        <v>69783257</v>
       </c>
       <c r="E12" t="n">
-        <v>11371245</v>
+        <v>11358677</v>
       </c>
       <c r="F12" t="n">
         <v>583243</v>
@@ -7937,16 +8228,16 @@
         <v>41805</v>
       </c>
       <c r="H12" t="n">
-        <v>18146389</v>
+        <v>20519208</v>
       </c>
       <c r="I12" t="n">
-        <v>5600653</v>
+        <v>5701998</v>
       </c>
       <c r="J12" t="n">
-        <v>82344186</v>
+        <v>90885709</v>
       </c>
       <c r="K12" t="n">
-        <v>12671826</v>
+        <v>12852816</v>
       </c>
     </row>
     <row r="13">
@@ -7966,10 +8257,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="E13" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="F13" t="n">
         <v>46536920</v>
@@ -7978,16 +8269,16 @@
         <v>4919974</v>
       </c>
       <c r="H13" t="n">
-        <v>2657716267</v>
+        <v>2792915906</v>
       </c>
       <c r="I13" t="n">
-        <v>594860354</v>
+        <v>596298298</v>
       </c>
       <c r="J13" t="n">
-        <v>7518596271</v>
+        <v>9581926087</v>
       </c>
       <c r="K13" t="n">
-        <v>746971977</v>
+        <v>773883343</v>
       </c>
     </row>
     <row r="14">
@@ -8007,10 +8298,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4814343</v>
+        <v>6742473</v>
       </c>
       <c r="E14" t="n">
-        <v>478704</v>
+        <v>553197</v>
       </c>
       <c r="F14" t="n">
         <v>46537</v>
@@ -8019,16 +8310,16 @@
         <v>4920</v>
       </c>
       <c r="H14" t="n">
-        <v>2657716</v>
+        <v>2792916</v>
       </c>
       <c r="I14" t="n">
-        <v>594860</v>
+        <v>596298</v>
       </c>
       <c r="J14" t="n">
-        <v>7518596</v>
+        <v>9581926</v>
       </c>
       <c r="K14" t="n">
-        <v>746972</v>
+        <v>773883</v>
       </c>
     </row>
     <row r="15">
@@ -8048,10 +8339,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="E15" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8060,16 +8351,16 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2657716267</v>
+        <v>2792915906</v>
       </c>
       <c r="I15" t="n">
-        <v>594860354</v>
+        <v>596298298</v>
       </c>
       <c r="J15" t="n">
-        <v>7472059351</v>
+        <v>9535389168</v>
       </c>
       <c r="K15" t="n">
-        <v>747079658</v>
+        <v>774238862</v>
       </c>
     </row>
     <row r="16">
@@ -8089,10 +8380,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4814343</v>
+        <v>6742473</v>
       </c>
       <c r="E16" t="n">
-        <v>478704</v>
+        <v>553197</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8101,16 +8392,16 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2657716</v>
+        <v>2792916</v>
       </c>
       <c r="I16" t="n">
-        <v>594860</v>
+        <v>596298</v>
       </c>
       <c r="J16" t="n">
-        <v>7472059</v>
+        <v>9535389</v>
       </c>
       <c r="K16" t="n">
-        <v>747080</v>
+        <v>774239</v>
       </c>
     </row>
     <row r="17">
@@ -8130,10 +8421,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>187.1</v>
+        <v>233.76</v>
       </c>
       <c r="E17" t="n">
-        <v>23.71</v>
+        <v>24.73</v>
       </c>
       <c r="F17" t="n">
         <v>1.9</v>
@@ -8142,16 +8433,16 @@
         <v>0.14</v>
       </c>
       <c r="H17" t="n">
-        <v>100.14</v>
+        <v>106.09</v>
       </c>
       <c r="I17" t="n">
-        <v>21.53</v>
+        <v>21.52</v>
       </c>
       <c r="J17" t="n">
-        <v>289.14</v>
+        <v>341.75</v>
       </c>
       <c r="K17" t="n">
-        <v>31.15</v>
+        <v>31.9</v>
       </c>
     </row>
   </sheetData>
@@ -8334,10 +8625,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>18146388938</v>
+        <v>20519208398</v>
       </c>
       <c r="P2" t="n">
-        <v>5600653216</v>
+        <v>5701998488</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -8346,19 +8637,19 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>18729632338</v>
+        <v>21102451797</v>
       </c>
       <c r="T2" t="n">
-        <v>5595907067</v>
+        <v>5698082190</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>18729632338</v>
+        <v>21102451797</v>
       </c>
       <c r="W2" t="n">
-        <v>5595907067</v>
+        <v>5698082190</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -8384,10 +8675,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H3" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -8420,19 +8711,19 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>6407992251</v>
+        <v>7024862635</v>
       </c>
       <c r="T3" t="n">
-        <v>1137086053</v>
+        <v>1135805037</v>
       </c>
       <c r="U3" t="n">
         <v>0.93457944</v>
       </c>
       <c r="V3" t="n">
-        <v>5988777804</v>
+        <v>6565292182</v>
       </c>
       <c r="W3" t="n">
-        <v>1062697245</v>
+        <v>1061500035</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -8458,16 +8749,16 @@
         <v>5123520</v>
       </c>
       <c r="G4" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H4" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I4" t="n">
-        <v>481434308</v>
+        <v>674247326</v>
       </c>
       <c r="J4" t="n">
-        <v>47870362</v>
+        <v>55319705</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -8488,25 +8779,25 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1873382511</v>
+        <v>1904911233</v>
       </c>
       <c r="R4" t="n">
-        <v>591914530</v>
+        <v>591185079</v>
       </c>
       <c r="S4" t="n">
-        <v>8762809070</v>
+        <v>9604021194</v>
       </c>
       <c r="T4" t="n">
-        <v>1246106403</v>
+        <v>1250659147</v>
       </c>
       <c r="U4" t="n">
         <v>0.8734387300000001</v>
       </c>
       <c r="V4" t="n">
-        <v>7653776810</v>
+        <v>8388524058</v>
       </c>
       <c r="W4" t="n">
-        <v>1088397592</v>
+        <v>1092374135</v>
       </c>
       <c r="X4" t="n">
         <v>4475081</v>
@@ -8532,16 +8823,16 @@
         <v>10247040</v>
       </c>
       <c r="G5" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H5" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I5" t="n">
-        <v>962868617</v>
+        <v>1348494652</v>
       </c>
       <c r="J5" t="n">
-        <v>95740723</v>
+        <v>110639409</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8562,25 +8853,25 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1908509662</v>
+        <v>1940305785</v>
       </c>
       <c r="R5" t="n">
-        <v>592379261</v>
+        <v>591373697</v>
       </c>
       <c r="S5" t="n">
-        <v>9279370530</v>
+        <v>10313663072</v>
       </c>
       <c r="T5" t="n">
-        <v>1275093102</v>
+        <v>1281532064</v>
       </c>
       <c r="U5" t="n">
         <v>0.81629788</v>
       </c>
       <c r="V5" t="n">
-        <v>7574730462</v>
+        <v>8419021269</v>
       </c>
       <c r="W5" t="n">
-        <v>1040855792</v>
+        <v>1046111903</v>
       </c>
       <c r="X5" t="n">
         <v>8364637</v>
@@ -8606,16 +8897,16 @@
         <v>15370560</v>
       </c>
       <c r="G6" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H6" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I6" t="n">
-        <v>1444302925</v>
+        <v>2022741979</v>
       </c>
       <c r="J6" t="n">
-        <v>143611085</v>
+        <v>165959114</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -8636,25 +8927,25 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1943391412</v>
+        <v>1975454937</v>
       </c>
       <c r="R6" t="n">
-        <v>592878582</v>
+        <v>591589483</v>
       </c>
       <c r="S6" t="n">
-        <v>9795686588</v>
+        <v>11023059550</v>
       </c>
       <c r="T6" t="n">
-        <v>1305177521</v>
+        <v>1314019988</v>
       </c>
       <c r="U6" t="n">
         <v>0.76289521</v>
       </c>
       <c r="V6" t="n">
-        <v>7473082397</v>
+        <v>8409439353</v>
       </c>
       <c r="W6" t="n">
-        <v>995713682</v>
+        <v>1002459557</v>
       </c>
       <c r="X6" t="n">
         <v>11726127</v>
@@ -8680,16 +8971,16 @@
         <v>20494080</v>
       </c>
       <c r="G7" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H7" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I7" t="n">
-        <v>1925737234</v>
+        <v>2696989305</v>
       </c>
       <c r="J7" t="n">
-        <v>191481447</v>
+        <v>221278819</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -8710,25 +9001,25 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1971976010</v>
+        <v>2004425744</v>
       </c>
       <c r="R7" t="n">
-        <v>593275852</v>
+        <v>591632559</v>
       </c>
       <c r="S7" t="n">
-        <v>10305705494</v>
+        <v>11726277683</v>
       </c>
       <c r="T7" t="n">
-        <v>1336340593</v>
+        <v>1347962537</v>
       </c>
       <c r="U7" t="n">
         <v>0.71298618</v>
       </c>
       <c r="V7" t="n">
-        <v>7347825587</v>
+        <v>8360673925</v>
       </c>
       <c r="W7" t="n">
-        <v>952792374</v>
+        <v>961078659</v>
       </c>
       <c r="X7" t="n">
         <v>14611996</v>
@@ -8754,16 +9045,16 @@
         <v>25617600</v>
       </c>
       <c r="G8" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H8" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I8" t="n">
-        <v>2407171542</v>
+        <v>3371236631</v>
       </c>
       <c r="J8" t="n">
-        <v>239351809</v>
+        <v>276598523</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8784,25 +9075,25 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2006595475</v>
+        <v>2039312610</v>
       </c>
       <c r="R8" t="n">
-        <v>593851691</v>
+        <v>591909124</v>
       </c>
       <c r="S8" t="n">
-        <v>10821759268</v>
+        <v>12435411875</v>
       </c>
       <c r="T8" t="n">
-        <v>1368422235</v>
+        <v>1383350360</v>
       </c>
       <c r="U8" t="n">
         <v>0.66634222</v>
       </c>
       <c r="V8" t="n">
-        <v>7210995136</v>
+        <v>8286240003</v>
       </c>
       <c r="W8" t="n">
-        <v>911837515</v>
+        <v>921784755</v>
       </c>
       <c r="X8" t="n">
         <v>17070089</v>
@@ -8828,16 +9119,16 @@
         <v>30741120</v>
       </c>
       <c r="G9" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H9" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I9" t="n">
-        <v>2888605851</v>
+        <v>4045483957</v>
       </c>
       <c r="J9" t="n">
-        <v>287222170</v>
+        <v>331918228</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -8858,25 +9149,25 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2275589461</v>
+        <v>2313123650</v>
       </c>
       <c r="R9" t="n">
-        <v>593672470</v>
+        <v>595647881</v>
       </c>
       <c r="S9" t="n">
-        <v>11572187562</v>
+        <v>13383470242</v>
       </c>
       <c r="T9" t="n">
-        <v>1400076054</v>
+        <v>1421135200</v>
       </c>
       <c r="U9" t="n">
         <v>0.6227497400000001</v>
       </c>
       <c r="V9" t="n">
-        <v>7206576817</v>
+        <v>8334552639</v>
       </c>
       <c r="W9" t="n">
-        <v>871897001</v>
+        <v>885011579</v>
       </c>
       <c r="X9" t="n">
         <v>19144025</v>
@@ -8902,16 +9193,16 @@
         <v>35864640</v>
       </c>
       <c r="G10" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H10" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I10" t="n">
-        <v>3370040159</v>
+        <v>4719731283</v>
       </c>
       <c r="J10" t="n">
-        <v>335092532</v>
+        <v>387237933</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -8932,25 +9223,25 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2303908525</v>
+        <v>2341828923</v>
       </c>
       <c r="R10" t="n">
-        <v>594168811</v>
+        <v>595779682</v>
       </c>
       <c r="S10" t="n">
-        <v>12081940934</v>
+        <v>14086422841</v>
       </c>
       <c r="T10" t="n">
-        <v>1433980632</v>
+        <v>1458923278</v>
       </c>
       <c r="U10" t="n">
         <v>0.5820090999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>7031799625</v>
+        <v>8198426344</v>
       </c>
       <c r="W10" t="n">
-        <v>834589784</v>
+        <v>849106631</v>
       </c>
       <c r="X10" t="n">
         <v>20873547</v>
@@ -8976,16 +9267,16 @@
         <v>40988160</v>
       </c>
       <c r="G11" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H11" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I11" t="n">
-        <v>3851474467</v>
+        <v>5393978609</v>
       </c>
       <c r="J11" t="n">
-        <v>382962894</v>
+        <v>442557638</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -9006,25 +9297,25 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2338313424</v>
+        <v>2376501224</v>
       </c>
       <c r="R11" t="n">
-        <v>594852742</v>
+        <v>596163424</v>
       </c>
       <c r="S11" t="n">
-        <v>12597780142</v>
+        <v>14795342468</v>
       </c>
       <c r="T11" t="n">
-        <v>1468610635</v>
+        <v>1497881723</v>
       </c>
       <c r="U11" t="n">
         <v>0.5439337400000001</v>
       </c>
       <c r="V11" t="n">
-        <v>6852357701</v>
+        <v>8047686001</v>
       </c>
       <c r="W11" t="n">
-        <v>798826879</v>
+        <v>814748412</v>
       </c>
       <c r="X11" t="n">
         <v>22294843</v>
@@ -9050,16 +9341,16 @@
         <v>46111680</v>
       </c>
       <c r="G12" t="n">
-        <v>6361455331</v>
+        <v>6978325715</v>
       </c>
       <c r="H12" t="n">
-        <v>1137124524</v>
+        <v>1135867675</v>
       </c>
       <c r="I12" t="n">
-        <v>4332908776</v>
+        <v>6068225936</v>
       </c>
       <c r="J12" t="n">
-        <v>430833255</v>
+        <v>497877342</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -9080,25 +9371,25 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2372667435</v>
+        <v>2411122637</v>
       </c>
       <c r="R12" t="n">
-        <v>595580600</v>
+        <v>596583585</v>
       </c>
       <c r="S12" t="n">
-        <v>13113568462</v>
+        <v>15504211207</v>
       </c>
       <c r="T12" t="n">
-        <v>1503967789</v>
+        <v>1537865908</v>
       </c>
       <c r="U12" t="n">
         <v>0.50834929</v>
       </c>
       <c r="V12" t="n">
-        <v>6666273245</v>
+        <v>7881554792</v>
       </c>
       <c r="W12" t="n">
-        <v>764540961</v>
+        <v>781773046</v>
       </c>
       <c r="X12" t="n">
         <v>23440840</v>
@@ -9130,10 +9421,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J13" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9154,25 +9445,25 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2406976755</v>
+        <v>2445699358</v>
       </c>
       <c r="R13" t="n">
-        <v>596352554</v>
+        <v>597040424</v>
       </c>
       <c r="S13" t="n">
-        <v>7221319839</v>
+        <v>9188172619</v>
       </c>
       <c r="T13" t="n">
-        <v>748315075</v>
+        <v>776618248</v>
       </c>
       <c r="U13" t="n">
         <v>0.4750928</v>
       </c>
       <c r="V13" t="n">
-        <v>3430797036</v>
+        <v>4365234623</v>
       </c>
       <c r="W13" t="n">
-        <v>355519102</v>
+        <v>368965735</v>
       </c>
       <c r="X13" t="n">
         <v>24341474</v>
@@ -9204,10 +9495,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J14" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -9228,25 +9519,25 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R14" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S14" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T14" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U14" t="n">
         <v>0.44401196</v>
       </c>
       <c r="V14" t="n">
-        <v>3277160470</v>
+        <v>4151203996</v>
       </c>
       <c r="W14" t="n">
-        <v>332141249</v>
+        <v>345845847</v>
       </c>
       <c r="X14" t="n">
         <v>22749042</v>
@@ -9278,10 +9569,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J15" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -9302,25 +9593,25 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R15" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S15" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T15" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U15" t="n">
         <v>0.41496445</v>
       </c>
       <c r="V15" t="n">
-        <v>3062766794</v>
+        <v>3879629903</v>
       </c>
       <c r="W15" t="n">
-        <v>310412382</v>
+        <v>323220418</v>
       </c>
       <c r="X15" t="n">
         <v>21260786</v>
@@ -9352,10 +9643,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J16" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -9376,25 +9667,25 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R16" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S16" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T16" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U16" t="n">
         <v>0.38781724</v>
       </c>
       <c r="V16" t="n">
-        <v>2862398873</v>
+        <v>3625822339</v>
       </c>
       <c r="W16" t="n">
-        <v>290105030</v>
+        <v>302075157</v>
       </c>
       <c r="X16" t="n">
         <v>19869894</v>
@@ -9426,10 +9717,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J17" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -9450,25 +9741,25 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R17" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S17" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T17" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U17" t="n">
         <v>0.36244602</v>
       </c>
       <c r="V17" t="n">
-        <v>2675139134</v>
+        <v>3388619009</v>
       </c>
       <c r="W17" t="n">
-        <v>271126196</v>
+        <v>282313231</v>
       </c>
       <c r="X17" t="n">
         <v>18569994</v>
@@ -9500,10 +9791,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J18" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -9524,25 +9815,25 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R18" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S18" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T18" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U18" t="n">
         <v>0.3387346</v>
       </c>
       <c r="V18" t="n">
-        <v>2500130032</v>
+        <v>3166933653</v>
       </c>
       <c r="W18" t="n">
-        <v>253388968</v>
+        <v>263844141</v>
       </c>
       <c r="X18" t="n">
         <v>17355135</v>
@@ -9574,10 +9865,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J19" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -9598,25 +9889,25 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R19" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S19" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T19" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U19" t="n">
         <v>0.31657439</v>
       </c>
       <c r="V19" t="n">
-        <v>2336570123</v>
+        <v>2959751077</v>
       </c>
       <c r="W19" t="n">
-        <v>236812120</v>
+        <v>246583309</v>
       </c>
       <c r="X19" t="n">
         <v>16219752</v>
@@ -9648,10 +9939,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J20" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -9672,25 +9963,25 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R20" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S20" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T20" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U20" t="n">
         <v>0.29586392</v>
       </c>
       <c r="V20" t="n">
-        <v>2183710395</v>
+        <v>2766122502</v>
       </c>
       <c r="W20" t="n">
-        <v>221319738</v>
+        <v>230451691</v>
       </c>
       <c r="X20" t="n">
         <v>15158647</v>
@@ -9722,10 +10013,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J21" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -9746,25 +10037,25 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R21" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S21" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T21" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U21" t="n">
         <v>0.27650833</v>
       </c>
       <c r="V21" t="n">
-        <v>2040850837</v>
+        <v>2585161217</v>
       </c>
       <c r="W21" t="n">
-        <v>206840877</v>
+        <v>215375412</v>
       </c>
       <c r="X21" t="n">
         <v>14166960</v>
@@ -9796,10 +10087,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J22" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -9820,25 +10111,25 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R22" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S22" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T22" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U22" t="n">
         <v>0.258419</v>
       </c>
       <c r="V22" t="n">
-        <v>1907337231</v>
+        <v>2416038521</v>
       </c>
       <c r="W22" t="n">
-        <v>193309231</v>
+        <v>201285432</v>
       </c>
       <c r="X22" t="n">
         <v>13240149</v>
@@ -9870,10 +10161,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J23" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -9894,25 +10185,25 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R23" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S23" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T23" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U23" t="n">
         <v>0.24151309</v>
       </c>
       <c r="V23" t="n">
-        <v>1782558159</v>
+        <v>2257979926</v>
       </c>
       <c r="W23" t="n">
-        <v>180662833</v>
+        <v>188117226</v>
       </c>
       <c r="X23" t="n">
         <v>12373971</v>
@@ -9944,10 +10235,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J24" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -9968,25 +10259,25 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R24" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S24" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T24" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U24" t="n">
         <v>0.22571317</v>
       </c>
       <c r="V24" t="n">
-        <v>1665942205</v>
+        <v>2110261613</v>
       </c>
       <c r="W24" t="n">
-        <v>168843769</v>
+        <v>175810492</v>
       </c>
       <c r="X24" t="n">
         <v>11564459</v>
@@ -10018,10 +10309,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J25" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -10042,25 +10333,25 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R25" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S25" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T25" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U25" t="n">
         <v>0.21094688</v>
       </c>
       <c r="V25" t="n">
-        <v>1556955332</v>
+        <v>1972207115</v>
       </c>
       <c r="W25" t="n">
-        <v>157797915</v>
+        <v>164308871</v>
       </c>
       <c r="X25" t="n">
         <v>10807906</v>
@@ -10092,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J26" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -10116,25 +10407,25 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R26" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S26" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T26" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U26" t="n">
         <v>0.19714662</v>
       </c>
       <c r="V26" t="n">
-        <v>1455098441</v>
+        <v>1843184220</v>
       </c>
       <c r="W26" t="n">
-        <v>147474687</v>
+        <v>153559692</v>
       </c>
       <c r="X26" t="n">
         <v>10100847</v>
@@ -10166,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J27" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -10190,25 +10481,25 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R27" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S27" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T27" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U27" t="n">
         <v>0.18424918</v>
       </c>
       <c r="V27" t="n">
-        <v>1359905085</v>
+        <v>1722602074</v>
       </c>
       <c r="W27" t="n">
-        <v>137826810</v>
+        <v>143513731</v>
       </c>
       <c r="X27" t="n">
         <v>9440043</v>
@@ -10240,10 +10531,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J28" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -10264,25 +10555,25 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R28" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S28" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T28" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U28" t="n">
         <v>0.17219549</v>
       </c>
       <c r="V28" t="n">
-        <v>1270939332</v>
+        <v>1609908481</v>
       </c>
       <c r="W28" t="n">
-        <v>128810103</v>
+        <v>134124982</v>
       </c>
       <c r="X28" t="n">
         <v>8822471</v>
@@ -10314,10 +10605,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J29" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10338,25 +10629,25 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R29" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S29" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T29" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U29" t="n">
         <v>0.16093037</v>
       </c>
       <c r="V29" t="n">
-        <v>1187793768</v>
+        <v>1504587365</v>
       </c>
       <c r="W29" t="n">
-        <v>120383274</v>
+        <v>125350451</v>
       </c>
       <c r="X29" t="n">
         <v>8245300</v>
@@ -10388,10 +10679,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J30" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -10412,25 +10703,25 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R30" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S30" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T30" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U30" t="n">
         <v>0.15040221</v>
       </c>
       <c r="V30" t="n">
-        <v>1110087634</v>
+        <v>1406156416</v>
       </c>
       <c r="W30" t="n">
-        <v>112507732</v>
+        <v>117149954</v>
       </c>
       <c r="X30" t="n">
         <v>7705887</v>
@@ -10462,10 +10753,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J31" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10486,25 +10777,25 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R31" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S31" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T31" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U31" t="n">
         <v>0.14056282</v>
       </c>
       <c r="V31" t="n">
-        <v>1037465078</v>
+        <v>1314164875</v>
       </c>
       <c r="W31" t="n">
-        <v>105147413</v>
+        <v>109485938</v>
       </c>
       <c r="X31" t="n">
         <v>7201764</v>
@@ -10536,10 +10827,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J32" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10560,25 +10851,25 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R32" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S32" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T32" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U32" t="n">
         <v>0.13136712</v>
       </c>
       <c r="V32" t="n">
-        <v>969593531</v>
+        <v>1228191472</v>
       </c>
       <c r="W32" t="n">
-        <v>98268611</v>
+        <v>102323307</v>
       </c>
       <c r="X32" t="n">
         <v>6730621</v>
@@ -10610,10 +10901,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J33" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -10634,25 +10925,25 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R33" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S33" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T33" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U33" t="n">
         <v>0.12277301</v>
       </c>
       <c r="V33" t="n">
-        <v>906162179</v>
+        <v>1147842497</v>
       </c>
       <c r="W33" t="n">
-        <v>91839823</v>
+        <v>95629259</v>
       </c>
       <c r="X33" t="n">
         <v>6290300</v>
@@ -10684,10 +10975,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J34" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -10708,25 +10999,25 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R34" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S34" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T34" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U34" t="n">
         <v>0.11474113</v>
       </c>
       <c r="V34" t="n">
-        <v>846880541</v>
+        <v>1072749997</v>
       </c>
       <c r="W34" t="n">
-        <v>85831610</v>
+        <v>89373139</v>
       </c>
       <c r="X34" t="n">
         <v>5878785</v>
@@ -10758,10 +11049,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J35" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10782,25 +11073,25 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R35" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S35" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T35" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U35" t="n">
         <v>0.1072347</v>
       </c>
       <c r="V35" t="n">
-        <v>791477141</v>
+        <v>1002570091</v>
       </c>
       <c r="W35" t="n">
-        <v>80216458</v>
+        <v>83526298</v>
       </c>
       <c r="X35" t="n">
         <v>5494191</v>
@@ -10832,10 +11123,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J36" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -10856,25 +11147,25 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R36" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S36" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T36" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U36" t="n">
         <v>0.10021934</v>
       </c>
       <c r="V36" t="n">
-        <v>739698262</v>
+        <v>936981393</v>
       </c>
       <c r="W36" t="n">
-        <v>74968653</v>
+        <v>78061961</v>
       </c>
       <c r="X36" t="n">
         <v>5134758</v>
@@ -10906,10 +11197,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J37" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -10930,25 +11221,25 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R37" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S37" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T37" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U37" t="n">
         <v>0.09366294</v>
       </c>
       <c r="V37" t="n">
-        <v>691306787</v>
+        <v>875683545</v>
       </c>
       <c r="W37" t="n">
-        <v>70064161</v>
+        <v>72955104</v>
       </c>
       <c r="X37" t="n">
         <v>4798839</v>
@@ -10980,10 +11271,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J38" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -11004,25 +11295,25 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R38" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S38" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T38" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U38" t="n">
         <v>0.08753546</v>
       </c>
       <c r="V38" t="n">
-        <v>646081110</v>
+        <v>818395837</v>
       </c>
       <c r="W38" t="n">
-        <v>65480525</v>
+        <v>68182340</v>
       </c>
       <c r="X38" t="n">
         <v>4484897</v>
@@ -11054,10 +11345,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J39" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -11078,25 +11369,25 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R39" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S39" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T39" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U39" t="n">
         <v>0.08180883999999999</v>
       </c>
       <c r="V39" t="n">
-        <v>603814121</v>
+        <v>764855922</v>
       </c>
       <c r="W39" t="n">
-        <v>61196752</v>
+        <v>63721813</v>
       </c>
       <c r="X39" t="n">
         <v>4191492</v>
@@ -11128,10 +11419,10 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J40" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -11152,25 +11443,25 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R40" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S40" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T40" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U40" t="n">
         <v>0.07645686</v>
       </c>
       <c r="V40" t="n">
-        <v>564312263</v>
+        <v>714818619</v>
       </c>
       <c r="W40" t="n">
-        <v>57193226</v>
+        <v>59553096</v>
       </c>
       <c r="X40" t="n">
         <v>3917282</v>
@@ -11202,10 +11493,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J41" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11226,25 +11517,25 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R41" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S41" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T41" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U41" t="n">
         <v>0.07145501</v>
       </c>
       <c r="V41" t="n">
-        <v>527394638</v>
+        <v>668054784</v>
       </c>
       <c r="W41" t="n">
-        <v>53451613</v>
+        <v>55657099</v>
       </c>
       <c r="X41" t="n">
         <v>3661012</v>
@@ -11276,10 +11567,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J42" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -11300,25 +11591,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2566450162</v>
+        <v>2606833463</v>
       </c>
       <c r="R42" t="n">
-        <v>595767931</v>
+        <v>599926945</v>
       </c>
       <c r="S42" t="n">
-        <v>7380793246</v>
+        <v>9349306724</v>
       </c>
       <c r="T42" t="n">
-        <v>748045727</v>
+        <v>778911108</v>
       </c>
       <c r="U42" t="n">
         <v>0.06678038</v>
       </c>
       <c r="V42" t="n">
-        <v>492892185</v>
+        <v>624350265</v>
       </c>
       <c r="W42" t="n">
-        <v>49954779</v>
+        <v>52015981</v>
       </c>
       <c r="X42" t="n">
         <v>3421506</v>
@@ -11350,10 +11641,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>4814343084</v>
+        <v>6742473262</v>
       </c>
       <c r="J43" t="n">
-        <v>478703617</v>
+        <v>553197047</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -11374,25 +11665,25 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2722237728</v>
+        <v>2763953614</v>
       </c>
       <c r="R43" t="n">
-        <v>595206777</v>
+        <v>602812618</v>
       </c>
       <c r="S43" t="n">
-        <v>7536580813</v>
+        <v>9506426875</v>
       </c>
       <c r="T43" t="n">
-        <v>747873890</v>
+        <v>781263573</v>
       </c>
       <c r="U43" t="n">
         <v>0.06241157</v>
       </c>
       <c r="V43" t="n">
-        <v>470369849</v>
+        <v>593311036</v>
       </c>
       <c r="W43" t="n">
-        <v>46675984</v>
+        <v>48759887</v>
       </c>
       <c r="X43" t="n">
         <v>3197669</v>
@@ -11424,10 +11715,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>4332908776</v>
+        <v>6068225936</v>
       </c>
       <c r="J44" t="n">
-        <v>430833255</v>
+        <v>497877342</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11448,25 +11739,25 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2532140842</v>
+        <v>2572256741</v>
       </c>
       <c r="R44" t="n">
-        <v>595006922</v>
+        <v>599466944</v>
       </c>
       <c r="S44" t="n">
-        <v>6865049618</v>
+        <v>8640482677</v>
       </c>
       <c r="T44" t="n">
-        <v>719564385</v>
+        <v>744156842</v>
       </c>
       <c r="U44" t="n">
         <v>0.05832857</v>
       </c>
       <c r="V44" t="n">
-        <v>400428535</v>
+        <v>503987008</v>
       </c>
       <c r="W44" t="n">
-        <v>41971162</v>
+        <v>43405605</v>
       </c>
       <c r="X44" t="n">
         <v>2689628</v>
@@ -11498,10 +11789,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>3851474467</v>
+        <v>5393978609</v>
       </c>
       <c r="J45" t="n">
-        <v>382962894</v>
+        <v>442557638</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -11522,25 +11813,25 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2497786831</v>
+        <v>2537635328</v>
       </c>
       <c r="R45" t="n">
-        <v>594290115</v>
+        <v>599043420</v>
       </c>
       <c r="S45" t="n">
-        <v>6349261298</v>
+        <v>7931613938</v>
       </c>
       <c r="T45" t="n">
-        <v>693229183</v>
+        <v>712063690</v>
       </c>
       <c r="U45" t="n">
         <v>0.05451268</v>
       </c>
       <c r="V45" t="n">
-        <v>346115270</v>
+        <v>432373558</v>
       </c>
       <c r="W45" t="n">
-        <v>37789783</v>
+        <v>38816502</v>
       </c>
       <c r="X45" t="n">
         <v>2234375</v>
@@ -11572,10 +11863,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3370040159</v>
+        <v>4719731283</v>
       </c>
       <c r="J46" t="n">
-        <v>335092532</v>
+        <v>387237933</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -11596,25 +11887,25 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2463381932</v>
+        <v>2502963028</v>
       </c>
       <c r="R46" t="n">
-        <v>593617342</v>
+        <v>598656112</v>
       </c>
       <c r="S46" t="n">
-        <v>5833422091</v>
+        <v>7222694311</v>
       </c>
       <c r="T46" t="n">
-        <v>669293287</v>
+        <v>683006904</v>
       </c>
       <c r="U46" t="n">
         <v>0.05094643</v>
       </c>
       <c r="V46" t="n">
-        <v>297192047</v>
+        <v>367970511</v>
       </c>
       <c r="W46" t="n">
-        <v>34098106</v>
+        <v>34796765</v>
       </c>
       <c r="X46" t="n">
         <v>1827175</v>
@@ -11646,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2888605851</v>
+        <v>4045483957</v>
       </c>
       <c r="J47" t="n">
-        <v>287222170</v>
+        <v>331918228</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -11670,25 +11961,25 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>2435062868</v>
+        <v>2474257755</v>
       </c>
       <c r="R47" t="n">
-        <v>593130853</v>
+        <v>598523180</v>
       </c>
       <c r="S47" t="n">
-        <v>5323668718</v>
+        <v>6519741712</v>
       </c>
       <c r="T47" t="n">
-        <v>648083641</v>
+        <v>657631979</v>
       </c>
       <c r="U47" t="n">
         <v>0.04761349</v>
       </c>
       <c r="V47" t="n">
-        <v>253478440</v>
+        <v>310427649</v>
       </c>
       <c r="W47" t="n">
-        <v>30857523</v>
+        <v>31312153</v>
       </c>
       <c r="X47" t="n">
         <v>1463692</v>
@@ -11720,10 +12011,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2407171542</v>
+        <v>3371236631</v>
       </c>
       <c r="J48" t="n">
-        <v>239351809</v>
+        <v>276598523</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -11744,25 +12035,25 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2400529054</v>
+        <v>2439456540</v>
       </c>
       <c r="R48" t="n">
-        <v>592541232</v>
+        <v>598202130</v>
       </c>
       <c r="S48" t="n">
-        <v>4807700597</v>
+        <v>5810693171</v>
       </c>
       <c r="T48" t="n">
-        <v>629757082</v>
+        <v>635865292</v>
       </c>
       <c r="U48" t="n">
         <v>0.04449859</v>
       </c>
       <c r="V48" t="n">
-        <v>213935886</v>
+        <v>258567639</v>
       </c>
       <c r="W48" t="n">
-        <v>28023301</v>
+        <v>28295107</v>
       </c>
       <c r="X48" t="n">
         <v>1139947</v>
@@ -11794,10 +12085,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1925737234</v>
+        <v>2696989305</v>
       </c>
       <c r="J49" t="n">
-        <v>191481447</v>
+        <v>221278819</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -11818,25 +12109,25 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2206436183</v>
+        <v>2243435569</v>
       </c>
       <c r="R49" t="n">
-        <v>592513012</v>
+        <v>595048486</v>
       </c>
       <c r="S49" t="n">
-        <v>4132173416</v>
+        <v>4940424874</v>
       </c>
       <c r="T49" t="n">
-        <v>615031507</v>
+        <v>615550645</v>
       </c>
       <c r="U49" t="n">
         <v>0.04158747</v>
       </c>
       <c r="V49" t="n">
-        <v>171846617</v>
+        <v>205459747</v>
       </c>
       <c r="W49" t="n">
-        <v>25577601</v>
+        <v>25599191</v>
       </c>
       <c r="X49" t="n">
         <v>852297</v>
@@ -11868,10 +12159,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1444302925</v>
+        <v>2022741979</v>
       </c>
       <c r="J50" t="n">
-        <v>143611085</v>
+        <v>165959114</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -11892,25 +12183,25 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2177851585</v>
+        <v>2214464763</v>
       </c>
       <c r="R50" t="n">
-        <v>592131672</v>
+        <v>595003435</v>
       </c>
       <c r="S50" t="n">
-        <v>3622154510</v>
+        <v>4237206741</v>
       </c>
       <c r="T50" t="n">
-        <v>603454799</v>
+        <v>602853320</v>
       </c>
       <c r="U50" t="n">
         <v>0.03886679</v>
       </c>
       <c r="V50" t="n">
-        <v>140781518</v>
+        <v>164686624</v>
       </c>
       <c r="W50" t="n">
-        <v>23454351</v>
+        <v>23430973</v>
       </c>
       <c r="X50" t="n">
         <v>597404</v>
@@ -11942,10 +12233,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>962868617</v>
+        <v>1348494652</v>
       </c>
       <c r="J51" t="n">
-        <v>95740723</v>
+        <v>110639409</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -11966,25 +12257,25 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2142969835</v>
+        <v>2179315611</v>
       </c>
       <c r="R51" t="n">
-        <v>591650017</v>
+        <v>594781278</v>
       </c>
       <c r="S51" t="n">
-        <v>3105838451</v>
+        <v>3527810263</v>
       </c>
       <c r="T51" t="n">
-        <v>595427174</v>
+        <v>594870811</v>
       </c>
       <c r="U51" t="n">
         <v>0.0363241</v>
       </c>
       <c r="V51" t="n">
-        <v>112816794</v>
+        <v>128144542</v>
       </c>
       <c r="W51" t="n">
-        <v>21628358</v>
+        <v>21608148</v>
       </c>
       <c r="X51" t="n">
         <v>372215</v>
@@ -12016,10 +12307,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>481434308</v>
+        <v>674247326</v>
       </c>
       <c r="J52" t="n">
-        <v>47870362</v>
+        <v>55319705</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -12040,25 +12331,25 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>2107842683</v>
+        <v>2143921058</v>
       </c>
       <c r="R52" t="n">
-        <v>591203126</v>
+        <v>594585843</v>
       </c>
       <c r="S52" t="n">
-        <v>2589276992</v>
+        <v>2818168385</v>
       </c>
       <c r="T52" t="n">
-        <v>591178455</v>
+        <v>592033001</v>
       </c>
       <c r="U52" t="n">
         <v>0.03394776</v>
       </c>
       <c r="V52" t="n">
-        <v>87900152</v>
+        <v>95670502</v>
       </c>
       <c r="W52" t="n">
-        <v>20069184</v>
+        <v>20098194</v>
       </c>
       <c r="X52" t="n">
         <v>173932</v>
@@ -12075,7 +12366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F394"/>
+  <dimension ref="A1:F396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16543,7 +16834,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>A75: Core Barrel Replacement Period (cycles)</t>
+          <t>A75: Inner Vessel Structure Replacement Period (cycles)</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -16556,7 +16847,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Number of fuel cycles between scheduled core barrel replacements</t>
+          <t>Number of fuel cycles between scheduled inner vessel structure replacements</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -16573,11 +16864,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>A75: Drum Replacement Period (cycles)</t>
+          <t>A75: Moderator Booster Replacement Period (cycles)</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -16586,7 +16877,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Number of fuel cycles between scheduled control drum replacements</t>
+          <t>Number of complete fuel cycles between moderator booster replacements</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -16603,11 +16894,11 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>A75: Reflector Replacement Period (cycles)</t>
+          <t>A75: Moderator Replacement Period (cycles)</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -16616,7 +16907,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Number of fuel cycles between scheduled reflector replacements</t>
+          <t>Number of complete fuel cycles between moderator replacements</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -16633,20 +16924,20 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>A75: Vessel Replacement Period (cycles)</t>
+          <t>A75: Outer Vessel Structure Replacement Period (years)</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>cycles</t>
+          <t>years</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Number of fuel cycles between scheduled reactor pressure vessel replacements</t>
+          <t>Service period in years between scheduled outer vessel structure replacements</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -16663,20 +16954,20 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>A78: CAPEX to Decommissioning Cost Ratio</t>
+          <t>A75: Reactor Control Devices Replacement Period (cycles)</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>0.15</v>
+        <v>2</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>cycles</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ratio of total decommissioning cost to total capital cost (typical range: 9%–15%)</t>
+          <t>Number of fuel cycles between scheduled reactor control device replacements</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -16693,25 +16984,25 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Annual Coolant Supply Frequency</t>
+          <t>A75: Reflector Replacement Period (cycles)</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>deliveries/year</t>
+          <t>cycles</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Number of coolant resupply deliveries per year (1 if purified, 6 if not)</t>
+          <t>Number of fuel cycles between scheduled reflector replacements</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -16723,25 +17014,25 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Annual Electricity Production</t>
+          <t>A78: CAPEX to Decommissioning Cost Ratio</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>51235.2</v>
+        <v>0.15</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>MWh/year</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Total annual electricity production at the calculated capacity factor</t>
+          <t>Ratio of total decommissioning cost to total capital cost (typical range: 9%–15%)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -16753,20 +17044,20 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Capacity Factor</t>
+          <t>Annual Coolant Supply Frequency</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>0.9747945205479452</v>
+        <v>4</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>deliveries/year</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Annual plant capacity factor — fraction of the year the plant operates at full power</t>
+          <t>Number of coolant resupply deliveries per year (1 if purified, 6 if not)</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -16783,25 +17074,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Emergency Shutdowns Per Year</t>
+          <t>Annual Electricity Production</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>0.2</v>
+        <v>51235.2</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>events/year</t>
+          <t>MWh/year</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Expected number of unplanned emergency shutdowns per year</t>
+          <t>Total annual electricity production at the calculated capacity factor</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -16813,25 +17104,25 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Levelization Period</t>
+          <t>Capacity Factor</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>40</v>
+        <v>0.9747945205479452</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Plant lifetime used for LCOE levelization (economic analysis period)</t>
+          <t>Annual plant capacity factor — fraction of the year the plant operates at full power</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -16843,20 +17134,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Maintenance to Direct Cost Ratio</t>
+          <t>Emergency Shutdowns Per Year</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>events/year</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ratio of annual non-replacement maintenance cost to total direct capital cost</t>
+          <t>Expected number of unplanned emergency shutdowns per year</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -16873,15 +17164,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Number of Operators</t>
+          <t>Levelization Period</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Number of operators assigned per shift</t>
+          <t>Plant lifetime used for LCOE levelization (economic analysis period)</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -16898,20 +17194,20 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Onsite Coolant Inventory</t>
+          <t>Maintenance to Direct Cost Ratio</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>49.5</v>
+        <v>0.03</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Total mass of coolant stored on site (fresh + used tanks)</t>
+          <t>Ratio of annual non-replacement maintenance cost to total direct capital cost</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -16928,17 +17224,15 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operation Mode</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Remotely Monitored</t>
-        </is>
+          <t>Number of On-Site Operators per Shift</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Reactor operation mode: Remotely Monitored or On-Site Staffed</t>
+          <t>Number of concurrent on-site operators assigned per shift</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -16955,15 +17249,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Reactors Monitored Per Operator</t>
+          <t>Onsite Coolant Inventory</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>9</v>
+        <v>49.5</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Number of reactors that can be monitored by a single operator</t>
+          <t>Total mass of coolant stored on site (fresh + used tanks)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -16980,20 +17279,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Refueling Period</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>30</v>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>days</t>
+          <t>Operation Mode</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>On-Site Staffed and Remotely Monitored</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Duration of the scheduled refueling outage</t>
+          <t>Reactor operation mode: Remotely Monitored, On-Site Staffed, or On-Site Staffed and Remotely Monitored</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -17010,20 +17306,15 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Replacement Coolant Inventory</t>
+          <t>Reactors Monitored Per Operator</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Mass of coolant replaced per refueling cycle</t>
+          <t>Number of reactors that can be monitored by a single operator</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -17040,15 +17331,20 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Security Staff Per Shift</t>
+          <t>Refueling Period</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Number of security personnel required per shift</t>
+          <t>Duration of the scheduled refueling outage</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -17065,20 +17361,20 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Startup Duration after Emergency Shutdown</t>
+          <t>Replacement Coolant Inventory</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>14</v>
+        <v>4.95</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Duration of the startup sequence following an emergency shutdown</t>
+          <t>Mass of coolant replaced per refueling cycle</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -17095,88 +17391,88 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Startup Duration after Refueling</t>
+          <t>Security Staff Per Shift</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>2</v>
-      </c>
-      <c r="D191" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Number of security personnel required per shift</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>User Input</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Startup Duration after Emergency Shutdown</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>14</v>
+      </c>
+      <c r="D192" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Duration of the startup sequence following a refueling outage</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Duration of the startup sequence following an emergency shutdown</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>User Input</t>
         </is>
       </c>
     </row>
-    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>--- ECONOMIC PARAMETERS ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Economic Parameters</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Annual Return</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>0.0475</v>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Annual return rate assumed for the decommissioning reserve fund</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Startup Duration after Refueling</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Duration of the startup sequence following a refueling outage</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>User Input</t>
         </is>
       </c>
     </row>
+    <row r="194"/>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Economic Parameters</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Assumed Number Of Units For Onsite Learning</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>200</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Number of units assumed for onsite learning (typically 2 × NOAK Unit Number)</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Calculated</t>
+          <t>--- ECONOMIC PARAMETERS ---</t>
         </is>
       </c>
     </row>
@@ -17188,20 +17484,20 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Construction Duration</t>
+          <t>Annual Return</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>12</v>
+        <v>0.0475</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Duration of plant construction used for financing cost calculation</t>
+          <t>Annual return rate assumed for the decommissioning reserve fund</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -17218,25 +17514,20 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Control Building Basement Volume</t>
+          <t>Assumed Number Of Units For Onsite Learning</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>5.9448192</v>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
+        <v>200</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Volume of concrete in the control building basement</t>
+          <t>Number of units assumed for onsite learning (typically 2 × NOAK Unit Number)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -17248,20 +17539,20 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Control Building Exterior Walls Volume</t>
+          <t>Construction Duration</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>14.207232</v>
+        <v>12</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>months</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Volume of concrete in the control building exterior walls</t>
+          <t>Duration of plant construction used for financing cost calculation</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -17278,7 +17569,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Control Building Slab Roof Volume</t>
+          <t>Control Building Basement Volume</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -17291,7 +17582,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Volume of concrete in the control building slab roof</t>
+          <t>Volume of concrete in the control building basement</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -17308,20 +17599,20 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Debt To Equity Ratio</t>
+          <t>Control Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>14.207232</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ratio of debt financing to equity financing for the project</t>
+          <t>Volume of concrete in the control building exterior walls</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -17338,20 +17629,20 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Discount Rate</t>
+          <t>Control Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.07000000000000001</v>
+        <v>5.9448192</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Annual discount rate (WACC) used for LCOE levelization and cost annualization</t>
+          <t>Volume of concrete in the control building slab roof</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -17368,20 +17659,20 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Emergency Building Basement Volume</t>
+          <t>Debt To Equity Ratio</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Volume of concrete in the emergency building basement (0 if none)</t>
+          <t>Ratio of debt financing to equity financing for the project</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -17398,20 +17689,20 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Emergency Building Exterior Walls Volume</t>
+          <t>Discount Rate</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Volume of concrete in the emergency building exterior walls (0 if none)</t>
+          <t>Annual discount rate (WACC) used for LCOE levelization and cost annualization</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -17428,7 +17719,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Emergency Building Slab Roof Volume</t>
+          <t>Emergency Building Basement Volume</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -17441,7 +17732,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Volume of concrete in the emergency building slab roof (0 if none)</t>
+          <t>Volume of concrete in the emergency building basement (0 if none)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -17458,20 +17749,20 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Escalation Year</t>
+          <t>Emergency Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>2025</v>
+        <v>0</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Reference year to which all costs are escalated for consistent comparison</t>
+          <t>Volume of concrete in the emergency building exterior walls (0 if none)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -17488,11 +17779,11 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Excavation Volume</t>
+          <t>Emergency Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>412.605</v>
+        <v>0</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17501,7 +17792,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Volume of earth to be excavated for plant construction</t>
+          <t>Volume of concrete in the emergency building slab roof (0 if none)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -17518,20 +17809,20 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>FTEs Per Offsite Operator (24/7)</t>
+          <t>Escalation Year</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>5</v>
+        <v>2025</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>FTE/operator</t>
+          <t>year</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Full-time equivalents needed per offsite operator position to maintain 24/7 coverage</t>
+          <t>Reference year to which all costs are escalated for consistent comparison</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -17548,20 +17839,20 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>FTEs Per Onsite Operator (24/7)</t>
+          <t>Excavation Volume</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>412.605</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>FTE/operator</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Full-time equivalents needed per onsite operator position to maintain 24/7 coverage</t>
+          <t>Volume of earth to be excavated for plant construction</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -17578,25 +17869,25 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>FTEs Per Onsite Operator Per Year</t>
+          <t>FTEs Per Offsite Operator (24/7)</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>0.01777777777777778</v>
+        <v>5</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>FTE/operator/year</t>
+          <t>FTE/operator</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Total FTE-years per operator per year including all activities</t>
+          <t>Full-time equivalents needed per offsite operator position to maintain 24/7 coverage</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -17608,20 +17899,20 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>FTEs Per Operator Per Year Per Refueling</t>
+          <t>FTEs Per Onsite Operator (24/7)</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>0.03333333333333333</v>
+        <v>5</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>FTE/operator/year</t>
+          <t>FTE/operator</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fraction of an FTE spent per operator per year on refueling-related activities</t>
+          <t>Full-time equivalents needed per onsite operator position to maintain 24/7 coverage</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -17638,7 +17929,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>FTEs Per Security Staff (24/7)</t>
+          <t>FTEs Per Onsite Operator Per Year</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -17646,17 +17937,17 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>FTE/staff</t>
+          <t>FTE/operator/year</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Full-time equivalents needed per security staff position to maintain 24/7 coverage</t>
+          <t>Total FTE-years per operator per year including all activities</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -17668,20 +17959,20 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Hours Per FTE</t>
+          <t>FTEs Per Operator Per Year Per Refueling</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1800</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>hours/year</t>
+          <t>FTE/operator/year</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Annual working hours per full-time equivalent employee</t>
+          <t>Fraction of an FTE spent per operator per year on refueling-related activities</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -17698,20 +17989,20 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Integrated Heat Exchanger Building Basement Volume</t>
+          <t>FTEs Per Security Staff (24/7)</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>FTE/staff</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Volume of concrete in the integrated heat exchanger building basement (0 if none)</t>
+          <t>Full-time equivalents needed per security staff position to maintain 24/7 coverage</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -17728,20 +18019,20 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Integrated Heat Exchanger Building Exterior Walls Volume</t>
+          <t>Hours Per FTE</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>hours/year</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Volume of concrete in the integrated heat exchanger building exterior walls (0 if none)</t>
+          <t>Annual working hours per full-time equivalent employee</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -17758,7 +18049,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Integrated Heat Exchanger Building Slab Roof Volume</t>
+          <t>Integrated Heat Exchanger Building Basement Volume</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -17771,7 +18062,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Volume of concrete in the integrated heat exchanger building slab roof (0 if none)</t>
+          <t>Volume of concrete in the integrated heat exchanger building basement (0 if none)</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -17788,7 +18079,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Integrated Heat Exchanger Building Superstructure Area</t>
+          <t>Integrated Heat Exchanger Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -17796,12 +18087,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Floor area of the integrated heat exchanger building superstructure (0 if none)</t>
+          <t>Volume of concrete in the integrated heat exchanger building exterior walls (0 if none)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -17818,20 +18109,20 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Integrated Heat Exchanger Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Annual cost of debt used to calculate interest during construction (Account 62)</t>
+          <t>Volume of concrete in the integrated heat exchanger building slab roof (0 if none)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -17848,20 +18139,20 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Land Area</t>
+          <t>Integrated Heat Exchanger Building Superstructure Area</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>acres</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Total land area required for the plant site</t>
+          <t>Floor area of the integrated heat exchanger building superstructure (0 if none)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -17878,20 +18169,20 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Manipulator Building Basement Volume</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>17.83738368</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Volume of concrete in the manipulator building basement</t>
+          <t>Annual cost of debt used to calculate interest during construction (Account 62)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -17908,20 +18199,20 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Manipulator Building Exterior Walls Volume</t>
+          <t>Land Area</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>15.9195008</v>
+        <v>18</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>acres</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Volume of concrete in the manipulator building exterior walls</t>
+          <t>Total land area required for the plant site</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -17938,11 +18229,11 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Manipulator Building Slab Roof Volume</t>
+          <t>Manipulator Building Basement Volume</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>4.756635648</v>
+        <v>17.83738368</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17951,7 +18242,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Volume of concrete in the manipulator building slab roof</t>
+          <t>Volume of concrete in the manipulator building basement</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -17968,15 +18259,20 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>NOAK Unit Number</t>
+          <t>Manipulator Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>100</v>
+        <v>15.9195008</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Nth-of-a-kind unit number used to calculate the learning curve cost multiplier</t>
+          <t>Volume of concrete in the manipulator building exterior walls</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -17993,15 +18289,20 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Number of Samples</t>
+          <t>Manipulator Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>100</v>
+        <v>4.756635648</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Number of Monte Carlo samples used for cost uncertainty quantification</t>
+          <t>Volume of concrete in the manipulator building slab roof</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -18018,20 +18319,15 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Radwaste Building Basement Volume</t>
+          <t>NOAK Unit Number</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>0</v>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
+        <v>100</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Volume of concrete in the radioactive waste building basement (0 if none)</t>
+          <t>Nth-of-a-kind unit number used to calculate the learning curve cost multiplier</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -18048,20 +18344,15 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Radwaste Building Exterior Walls Volume</t>
+          <t>Number of Samples</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
+        <v>100</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Volume of concrete in the radioactive waste building exterior walls (0 if none)</t>
+          <t>Number of Monte Carlo samples used for cost uncertainty quantification</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -18078,7 +18369,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Radwaste Building Slab Roof Volume</t>
+          <t>Radwaste Building Basement Volume</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -18091,7 +18382,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Volume of concrete in the radioactive waste building slab roof (0 if none)</t>
+          <t>Volume of concrete in the radioactive waste building basement (0 if none)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -18108,11 +18399,11 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Reactor Building Basement Volume</t>
+          <t>Radwaste Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>95.0976</v>
+        <v>0</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18121,7 +18412,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Volume of concrete in the reactor building basement</t>
+          <t>Volume of concrete in the radioactive waste building exterior walls (0 if none)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -18138,11 +18429,11 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Reactor Building Exterior Walls Volume</t>
+          <t>Radwaste Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>129.9564</v>
+        <v>0</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18151,7 +18442,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Volume of concrete in the reactor building exterior walls</t>
+          <t>Volume of concrete in the radioactive waste building slab roof (0 if none)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -18168,7 +18459,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Reactor Building Slab Roof Volume</t>
+          <t>Reactor Building Basement Volume</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -18181,7 +18472,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Volume of concrete in the reactor building slab roof</t>
+          <t>Volume of concrete in the reactor building basement</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18198,20 +18489,20 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Reactor Building Superstructure Area</t>
+          <t>Reactor Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>77</v>
+        <v>129.9564</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Floor area of the reactor building superstructure</t>
+          <t>Volume of concrete in the reactor building exterior walls</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -18228,11 +18519,11 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Refueling Building Basement Volume</t>
+          <t>Reactor Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>95.0976</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18241,7 +18532,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Volume of concrete in the refueling building basement (0 if none)</t>
+          <t>Volume of concrete in the reactor building slab roof</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -18258,20 +18549,20 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Refueling Building Exterior Walls Volume</t>
+          <t>Reactor Building Superstructure Area</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Volume of concrete in the refueling building exterior walls (0 if none)</t>
+          <t>Floor area of the reactor building superstructure</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -18288,7 +18579,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Refueling Building Slab Roof Volume</t>
+          <t>Refueling Building Basement Volume</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -18301,7 +18592,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Volume of concrete in the refueling building slab roof (0 if none)</t>
+          <t>Volume of concrete in the refueling building basement (0 if none)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -18318,7 +18609,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Spent Fuel Building Basement Volume</t>
+          <t>Refueling Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -18331,7 +18622,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Volume of concrete in the spent fuel building basement (0 if none)</t>
+          <t>Volume of concrete in the refueling building exterior walls (0 if none)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -18348,7 +18639,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Spent Fuel Building Exterior Walls Volume</t>
+          <t>Refueling Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -18361,7 +18652,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Volume of concrete in the spent fuel building exterior walls (0 if none)</t>
+          <t>Volume of concrete in the refueling building slab roof (0 if none)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -18378,7 +18669,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Spent Fuel Building Slab Roof Volume</t>
+          <t>Spent Fuel Building Basement Volume</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -18391,7 +18682,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Volume of concrete in the spent fuel building slab roof (0 if none)</t>
+          <t>Volume of concrete in the spent fuel building basement (0 if none)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -18408,11 +18699,11 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Storage Building Basement Volume</t>
+          <t>Spent Fuel Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>11.76</v>
+        <v>0</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18421,7 +18712,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Volume of concrete in the storage building basement</t>
+          <t>Volume of concrete in the spent fuel building exterior walls (0 if none)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -18438,11 +18729,11 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Storage Building Exterior Walls Volume</t>
+          <t>Spent Fuel Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>15.768</v>
+        <v>0</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18451,7 +18742,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Volume of concrete in the storage building exterior walls</t>
+          <t>Volume of concrete in the spent fuel building slab roof (0 if none)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -18468,7 +18759,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Storage Building Slab Roof Volume</t>
+          <t>Storage Building Basement Volume</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -18481,7 +18772,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Volume of concrete in the storage building slab roof (houses operational spares)</t>
+          <t>Volume of concrete in the storage building basement</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -18498,11 +18789,11 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Turbine Building Basement Volume</t>
+          <t>Storage Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>5.9448192</v>
+        <v>15.768</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18511,7 +18802,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Volume of concrete in the turbine building basement</t>
+          <t>Volume of concrete in the storage building exterior walls</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -18528,11 +18819,11 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Turbine Building Exterior Walls Volume</t>
+          <t>Storage Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>14.207232</v>
+        <v>11.76</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18541,7 +18832,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Volume of concrete in the turbine building exterior walls</t>
+          <t>Volume of concrete in the storage building slab roof (houses operational spares)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -18558,7 +18849,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Turbine Building Slab Roof Volume</t>
+          <t>Turbine Building Basement Volume</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -18571,7 +18862,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Volume of concrete in the turbine building slab roof</t>
+          <t>Volume of concrete in the turbine building basement</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -18588,20 +18879,20 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Work Hours Per Shift</t>
+          <t>Turbine Building Exterior Walls Volume</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>10</v>
+        <v>14.207232</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Duration of each work shift</t>
+          <t>Volume of concrete in the turbine building exterior walls</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -18618,20 +18909,20 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>indirect to direct field-related cost</t>
+          <t>Turbine Building Slab Roof Volume</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>0.06538993205254329</v>
+        <v>5.9448192</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Ratio of indirect field (site) costs to total direct field costs — covers site supervision, temporary facilities, and other indirect site activities</t>
+          <t>Volume of concrete in the turbine building slab roof</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -18640,71 +18931,71 @@
         </is>
       </c>
     </row>
-    <row r="245"/>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Economic Parameters</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Work Hours Per Shift</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>10</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Duration of each work shift</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>User Input</t>
+        </is>
+      </c>
+    </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>--- CENTRAL FACILITY ---</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Central Facility</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Annual Reactor Cask Replacement</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
-        <v>5</v>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>casks/year</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Annual replacement rate for reactor transport casks.</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
+          <t>Economic Parameters</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>indirect to direct field-related cost</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>0.06538993205254329</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Ratio of indirect field (site) costs to total direct field costs — covers site supervision, temporary facilities, and other indirect site activities</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
         <is>
           <t>User Input</t>
         </is>
       </c>
     </row>
+    <row r="247"/>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Central Facility</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Max Reactors Per Servicing Facility</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>reactors/facility</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Maximum number of reactors assigned to one servicing facility.</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>User Input</t>
+          <t>--- CENTRAL FACILITY ---</t>
         </is>
       </c>
     </row>
@@ -18716,15 +19007,20 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Reactor Transport Vehicle Count</t>
+          <t>Annual Reactor Cask Replacement</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>casks/year</t>
+        </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Number of vehicles for transporting reactor units to/from field sites.</t>
+          <t>Annual replacement rate for reactor transport casks.</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -18741,25 +19037,25 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Servicing Facility Count</t>
+          <t>Max Reactors Per Servicing Facility</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>reactors/facility</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Number of servicing facilities required for the fleet.</t>
+          <t>Maximum number of reactors assigned to one servicing facility.</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -18771,25 +19067,20 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Servicing Facility Design Capacity</t>
+          <t>Reactor Transport Vehicle Count</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>reactors/facility</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Standard facility capacity based on the largest assigned reactor count.</t>
+          <t>Number of vehicles for transporting reactor units to/from field sites.</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -18801,22 +19092,20 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Servicing Facility Reactor Counts</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>(1000,)</t>
-        </is>
+          <t>SER Operator FTEs Per Facility</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>248</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>reactors</t>
+          <t>FTE/facility</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Balanced whole-reactor allocation across servicing facilities.</t>
+          <t>Total annual operator FTE headcount for one servicing facility; used directly to calculate servicing-campus Account 711.</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18833,20 +19122,25 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Servicing Hot Cell Count</t>
+          <t>Servicing Facility Count</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>facilities</t>
+        </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Number of hot cells for reactor servicing operations.</t>
+          <t>Number of servicing facilities required for the fleet.</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -18858,20 +19152,20 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Servicing Rate Per Facility</t>
+          <t>Servicing Facility Design Capacity</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>200.9911894273128</v>
+        <v>1000</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>reactors/year/facility</t>
+          <t>reactors/facility</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Fleet servicing rate distributed evenly across facilities.</t>
+          <t>Standard facility capacity based on the largest assigned reactor count.</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -18880,101 +19174,98 @@
         </is>
       </c>
     </row>
-    <row r="255"/>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Central Facility</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Servicing Facility Reactor Counts</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>(1000,)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>reactors</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Balanced whole-reactor allocation across servicing facilities.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>--- LEARNING RATES ---</t>
+          <t>Central Facility</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Servicing Hot Cell Count</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Number of hot cells for reactor servicing operations.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>User Input</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Learning Rates</t>
+          <t>Central Facility</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Cask Learning Cap</t>
+          <t>Servicing Rate Per Facility</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>100</v>
+        <v>200.9911894273128</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>casks</t>
+          <t>reactors/year/facility</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Cask number after which unit-cost learning stops.</t>
+          <t>Fleet servicing rate distributed evenly across facilities.</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>User Input</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Learning Rates</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Cask Learning Rate</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>fraction per doubling</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Unit-cost reduction for each doubling of cask production experience.</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>User Input</t>
-        </is>
-      </c>
-    </row>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="258"/>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Learning Rates</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Factory Be</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>0.4150537767859926</v>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>Learning rate for factory-manufactured beryllium components</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>User Input</t>
+          <t>--- LEARNING RATES ---</t>
         </is>
       </c>
     </row>
@@ -18986,25 +19277,25 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Factory Be Cost Multiplier</t>
+          <t>Cask Learning Cap</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>0.02836297647058825</v>
+        <v>100</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>casks</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for beryllium components based on Wright's Law</t>
+          <t>Cask number after which unit-cost learning stops.</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19016,20 +19307,20 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Factory BeO</t>
+          <t>Cask Learning Rate</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>0.3991490581140172</v>
+        <v>0.15</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>fraction per doubling</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Learning rate for factory-manufactured beryllium oxide components</t>
+          <t>Unit-cost reduction for each doubling of cask production experience.</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -19046,11 +19337,11 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Factory BeO Cost Multiplier</t>
+          <t>Factory Be</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>0.03389675138437502</v>
+        <v>0.4150537767859926</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19059,12 +19350,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for beryllium oxide components based on Wright's Law</t>
+          <t>Learning rate for factory-manufactured beryllium components</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19076,11 +19367,11 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Factory Drums</t>
+          <t>Factory Be Cost Multiplier</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0.24138</v>
+        <v>0.02836297647058825</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19089,12 +19380,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Learning rate for factory-manufactured control drum components</t>
+          <t>NOAK cost multiplier for beryllium components based on Wright's Law</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19106,11 +19397,11 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Factory Drums Cost Multiplier</t>
+          <t>Factory BeO</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>0.159550666940931</v>
+        <v>0.3991490581140172</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19119,12 +19410,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for factory-built control drums based on Wright's Law</t>
+          <t>Learning rate for factory-manufactured beryllium oxide components</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19136,11 +19427,11 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Factory Other</t>
+          <t>Factory BeO Cost Multiplier</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>0.2296284802211553</v>
+        <v>0.03389675138437502</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19149,12 +19440,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Learning rate for other factory-manufactured components</t>
+          <t>NOAK cost multiplier for beryllium oxide components based on Wright's Law</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19166,11 +19457,11 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Factory Other Cost Multiplier</t>
+          <t>Factory Drums</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>0.1767065090656982</v>
+        <v>0.24138</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19179,12 +19470,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for other factory-built components based on Wright's Law</t>
+          <t>Learning rate for factory-manufactured control drum components</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19196,11 +19487,11 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Factory Primary Structure</t>
+          <t>Factory Drums Cost Multiplier</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>0.1844316982010974</v>
+        <v>0.159550666940931</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19209,12 +19500,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Learning rate for factory-manufactured primary structural components</t>
+          <t>NOAK cost multiplier for factory-built control drums based on Wright's Law</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19226,11 +19517,11 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Factory Primary Structure Cost Multiplier</t>
+          <t>Factory Other</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>0.2580805160204893</v>
+        <v>0.2296284802211553</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19239,12 +19530,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for factory-built primary structure based on Wright's Law</t>
+          <t>Learning rate for other factory-manufactured components</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19256,11 +19547,11 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Licensing Learning</t>
+          <t>Factory Other Cost Multiplier</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>0.2</v>
+        <v>0.1767065090656982</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19269,12 +19560,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Learning rate for licensing costs per doubling of cumulative units produced</t>
+          <t>NOAK cost multiplier for other factory-built components based on Wright's Law</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19286,11 +19577,11 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Licensing Learning Cost Multiplier</t>
+          <t>Factory Primary Structure</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>0.2270616608678975</v>
+        <v>0.1844316982010974</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19299,12 +19590,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for licensing costs based on Wright's Law</t>
+          <t>Learning rate for factory-manufactured primary structural components</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19316,11 +19607,11 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>No Learning</t>
+          <t>Factory Primary Structure Cost Multiplier</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>0.2580805160204893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19329,12 +19620,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Learning rate for components with no learning benefit (fixed costs, rate = 0)</t>
+          <t>NOAK cost multiplier for factory-built primary structure based on Wright's Law</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19346,11 +19637,11 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>No Learning Cost Multiplier</t>
+          <t>Licensing Learning</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19359,12 +19650,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for components with no learning (always 1.0)</t>
+          <t>Learning rate for licensing costs per doubling of cumulative units produced</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19376,11 +19667,11 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Non-nuclear off-the-shelf</t>
+          <t>Licensing Learning Cost Multiplier</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>0.05</v>
+        <v>0.2270616608678975</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19389,12 +19680,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Learning rate for non-nuclear commercial off-the-shelf components</t>
+          <t>NOAK cost multiplier for licensing costs based on Wright's Law</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19406,11 +19697,11 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Non-nuclear off-the-shelf Cost Multiplier</t>
+          <t>No Learning</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>0.711211609276759</v>
+        <v>0</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19419,12 +19710,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for non-nuclear commercial components based on Wright's Law</t>
+          <t>Learning rate for components with no learning benefit (fixed costs, rate = 0)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19436,11 +19727,11 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Onsite Learning</t>
+          <t>No Learning Cost Multiplier</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19449,12 +19740,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Learning rate for onsite construction and installation activities</t>
+          <t>NOAK cost multiplier for components with no learning (always 1.0)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19466,11 +19757,11 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Onsite Learning Cost Multiplier</t>
+          <t>Non-nuclear off-the-shelf</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>0.5746607463452651</v>
+        <v>0.05</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19479,12 +19770,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>NOAK cost multiplier for onsite construction activities based on Wright's Law</t>
+          <t>Learning rate for non-nuclear commercial off-the-shelf components</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19496,25 +19787,25 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Servicing Facility Learning Cap</t>
+          <t>Non-nuclear off-the-shelf Cost Multiplier</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>5</v>
+        <v>0.711211609276759</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>facilities</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Facility number after which servicing-facility OCC learning stops.</t>
+          <t>NOAK cost multiplier for non-nuclear commercial components based on Wright's Law</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
@@ -19526,13 +19817,11 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Servicing Facility OCC Learning Multipliers</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>(1.0,)</t>
-        </is>
+          <t>Onsite Learning</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>0.08</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19541,12 +19830,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Sequential OCC multiplier for each servicing facility.</t>
+          <t>Learning rate for onsite construction and installation activities</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Calculated</t>
+          <t>User Input</t>
         </is>
       </c>
     </row>
@@ -19558,108 +19847,125 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Servicing Facility OCC Learning Rate</t>
+          <t>Onsite Learning Cost Multiplier</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>0.3</v>
+        <v>0.5746607463452651</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>fraction per doubling</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>OCC reduction for each doubling of servicing-facility experience.</t>
+          <t>NOAK cost multiplier for onsite construction activities based on Wright's Law</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
+          <t>Calculated</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Learning Rates</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Servicing Facility Learning Cap</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>5</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>facilities</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Facility number after which servicing-facility OCC learning stops.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
           <t>User Input</t>
         </is>
       </c>
     </row>
-    <row r="280"/>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>--- UNCATEGORIZED ---</t>
+          <t>Learning Rates</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Servicing Facility OCC Learning Multipliers</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>(1.0,)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Sequential OCC multiplier for each servicing facility.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Calculated</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Learning Rates</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Annual Radwaste Cask Consumption</t>
+          <t>Servicing Facility OCC Learning Rate</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>100.4955947136564</v>
+        <v>0.3</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>fraction per doubling</t>
+        </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
+          <t>OCC reduction for each doubling of servicing-facility experience.</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Annual Used Fuel Cask Consumption</t>
-        </is>
-      </c>
-      <c r="C283" t="n">
-        <v>200.9911894273128</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-    </row>
+          <t>User Input</t>
+        </is>
+      </c>
+    </row>
+    <row r="283"/>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Average Distance From Serv to GenSite</t>
-        </is>
-      </c>
-      <c r="C284" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Unknown</t>
+          <t>--- UNCATEGORIZED ---</t>
         </is>
       </c>
     </row>
@@ -19671,11 +19977,11 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CoolantInventoryRPV_Mass</t>
+          <t>Annual Radwaste Cask Consumption</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>40.5125</v>
+        <v>100.4955947136564</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -19696,11 +20002,11 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Cycle Length</t>
+          <t>Annual Used Fuel Cask Consumption</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4.975342465753425</v>
+        <v>200.9911894273128</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -19721,11 +20027,11 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Deployment Period</t>
+          <t>Average Distance From Serv to GenSite</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -19746,11 +20052,11 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dwell Time GenSite</t>
+          <t>CoolantInventoryRPV_Mass</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>0.00273972602739726</v>
+        <v>40.5125</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -19771,11 +20077,11 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Dwell Time Reactor Transport GenSite</t>
+          <t>Cycle Length</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>0.005479452054794521</v>
+        <v>4.975342465753425</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -19796,11 +20102,11 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Dwell Time Reactor Transport Serv</t>
+          <t>Deployment Period</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>0.005479452054794521</v>
+        <v>10</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -19821,7 +20127,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dwell Time Serv</t>
+          <t>Dwell Time GenSite</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -19846,11 +20152,11 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Extra RPV Fraction</t>
+          <t>Dwell Time Reactor Transport GenSite</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>0.015</v>
+        <v>0.005479452054794521</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -19871,11 +20177,11 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Fleet</t>
+          <t>Dwell Time Reactor Transport Serv</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>1000</v>
+        <v>0.005479452054794521</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -19896,13 +20202,11 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Fleet Mode</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
+          <t>Dwell Time Serv</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>0.00273972602739726</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -19923,11 +20227,11 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Fuel Mass In Core</t>
+          <t>Extra RPV Fraction</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>569.8820389145857</v>
+        <v>0.015</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -19948,11 +20252,11 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>GenSite Downtime</t>
+          <t>Fleet</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>0.08333333333333333</v>
+        <v>1000</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -19973,11 +20277,13 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Generating Sites Count</t>
-        </is>
-      </c>
-      <c r="C297" t="n">
-        <v>973</v>
+          <t>Fleet Mode</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -19998,11 +20304,11 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>He Gas Replenishment</t>
+          <t>Fuel Mass In Core</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>19354.40556167401</v>
+        <v>569.8820389145857</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -20023,11 +20329,11 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>He Gas Replenishment Per Hot Cell</t>
+          <t>GenSite Downtime</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>3737.25</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -20048,11 +20354,11 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Helicopter Count</t>
+          <t>Generating Sites Count</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>2</v>
+        <v>973</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -20073,11 +20379,11 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Helium Purification and Storage Building Area</t>
+          <t>He Gas Replenishment</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>975.2897482236333</v>
+        <v>19354.40556167401</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -20098,11 +20404,11 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Helium Transport Truck Count</t>
+          <t>He Gas Replenishment Per Hot Cell</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>71</v>
+        <v>3737.25</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -20123,11 +20429,11 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MFG Account 223 to Reactor OCC per Testing Line Ratio</t>
+          <t>Helicopter Count</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -20148,11 +20454,11 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MFG Account 30 to Account 20 Ratio</t>
+          <t>Helium Purification and Storage Building Area</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>0.5</v>
+        <v>975.2897482236333</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -20173,11 +20479,11 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MFG Account 716 to Accounts 711-715 Ratio</t>
+          <t>Helium Transport Truck Count</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>0.02</v>
+        <v>71</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -20198,11 +20504,11 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MFG Account 717 to Accounts 711-715 Ratio</t>
+          <t>MFG Account 223 to Reactor OCC per Testing Line Ratio</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>0.075</v>
+        <v>0.1</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -20223,11 +20529,11 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MFG Account 741 to Account 20 Ratio</t>
+          <t>MFG Account 30 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>0.005</v>
+        <v>0.5</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -20248,11 +20554,11 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MFG Account 742 to Account 20 Ratio</t>
+          <t>MFG Account 716 to Accounts 711-715 Ratio</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -20273,11 +20579,11 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MFG Account 743 to Account 20 Ratio</t>
+          <t>MFG Account 717 to Accounts 711-715 Ratio</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>0.01</v>
+        <v>0.075</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -20298,11 +20604,11 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MFG Account 747.1 to Accounts 741-743 Ratio</t>
+          <t>MFG Account 741 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -20323,11 +20629,11 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MFG Account 747.4 to Account 20 Ratio</t>
+          <t>MFG Account 742 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -20348,11 +20654,11 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MFG Administration Building Area</t>
+          <t>MFG Account 743 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>4644.828205962553</v>
+        <v>0.01</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -20373,11 +20679,11 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MFG Campus Land Area</t>
+          <t>MFG Account 747.1 to Accounts 741-743 Ratio</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>63.49947854144788</v>
+        <v>0.05</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -20398,11 +20704,11 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MFG Campus Power</t>
+          <t>MFG Account 747.4 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>1.437599791893756</v>
+        <v>0.005</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -20423,11 +20729,11 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MFG Construction Duration</t>
+          <t>MFG Administration Building Area</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>36</v>
+        <v>4644.828205962553</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -20448,11 +20754,11 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MFG Emergency Generator Power</t>
+          <t>MFG Campus Land Area</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>4.999248694168273</v>
+        <v>63.49947854144788</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -20473,11 +20779,11 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MFG Fire Station Count</t>
+          <t>MFG Campus Power</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>1.437599791893756</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -20498,11 +20804,11 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MFG Guard Station Count</t>
+          <t>MFG Construction Duration</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -20523,11 +20829,11 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MFG Local Control Building Area</t>
+          <t>MFG Emergency Generator Power</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>80</v>
+        <v>4.999248694168273</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -20548,11 +20854,11 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MFG Local Transport Vehicle Count</t>
+          <t>MFG Fire Station Count</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -20573,11 +20879,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>MFG Maintenance Staff Headcount</t>
+          <t>MFG Guard Station Count</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -20598,11 +20904,11 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MFG Motion Detector Count</t>
+          <t>MFG Local Control Building Area</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -20623,11 +20929,11 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>MFG Protected Perimeter</t>
+          <t>MFG Local Transport Vehicle Count</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>1590.770544</v>
+        <v>2</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -20648,11 +20954,11 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>MFG Road Length</t>
+          <t>MFG Maintenance Staff Headcount</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>1828.802144730464</v>
+        <v>6</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -20673,11 +20979,11 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MFG Security Building Area</t>
+          <t>MFG Motion Detector Count</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>815.2440026135969</v>
+        <v>108</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -20698,11 +21004,11 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MFG Security Camera Count</t>
+          <t>MFG Protected Perimeter</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>67.99999999999793</v>
+        <v>1590.770544</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -20723,11 +21029,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MFG Security Staff Per Shift</t>
+          <t>MFG Road Length</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>6</v>
+        <v>1828.802144730464</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -20748,11 +21054,11 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>MFG Site Perimeter</t>
+          <t>MFG Security Building Area</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>1828.802144730464</v>
+        <v>815.2440026135969</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -20773,11 +21079,11 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>MFG Switchyard Rating</t>
+          <t>MFG Security Camera Count</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>3</v>
+        <v>67.99999999999793</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -20798,11 +21104,11 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>MFG Testing Coolant Allotment</t>
+          <t>MFG Security Staff Per Shift</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>153.81528129</v>
+        <v>6</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -20823,11 +21129,11 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>MFG Testing Engineering Headcount</t>
+          <t>MFG Site Perimeter</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>8</v>
+        <v>1828.802144730464</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -20848,11 +21154,11 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>MFG Testing Line Annual Rate</t>
+          <t>MFG Switchyard Rating</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -20873,11 +21179,11 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MFG Testing Line Count</t>
+          <t>MFG Testing Coolant Allotment</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>2</v>
+        <v>153.81528129</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -20898,11 +21204,11 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>MFG Testing Number of Operators</t>
+          <t>MFG Testing Engineering Headcount</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -20923,11 +21229,11 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>MFG Utility Vehicle Count</t>
+          <t>MFG Testing Line Annual Rate</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -20948,11 +21254,11 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MFG Warehouse Building Area</t>
+          <t>MFG Testing Line Count</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>6499.941419867174</v>
+        <v>2</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -20973,11 +21279,11 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MFG Warehouse Staff</t>
+          <t>MFG Testing Number of Operators</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -20998,11 +21304,11 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Maintenance Truck Count</t>
+          <t>MFG Utility Vehicle Count</t>
         </is>
       </c>
       <c r="C338" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -21023,11 +21329,11 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Maintenance Visit Frequency</t>
+          <t>MFG Warehouse Building Area</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>0.4019823788546256</v>
+        <v>6499.941419867174</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -21048,11 +21354,11 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Manufacturing Campus Area</t>
+          <t>MFG Warehouse Staff</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>63.49947854144788</v>
+        <v>7</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -21073,11 +21379,11 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Moderator Booster Mass ZrH</t>
+          <t>Maintenance Truck Count</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1351.136168455898</v>
+        <v>8</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -21098,11 +21404,11 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Parts Service Center and Warehouse Building Area</t>
+          <t>Maintenance Visit Frequency</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>8487.570829678751</v>
+        <v>0.4019823788546256</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -21123,11 +21429,11 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Production Rate</t>
+          <t>Manufacturing Campus Area</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>100</v>
+        <v>63.49947854144788</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -21148,11 +21454,11 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Radioactive Waste Processing Hot Cell Count</t>
+          <t>Moderator Booster Mass ZrH</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>1</v>
+        <v>1351.136168455898</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -21173,11 +21479,11 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Radwaste Storage Warehouses Area</t>
+          <t>Parts Service Center and Warehouse Building Area</t>
         </is>
       </c>
       <c r="C345" t="n">
-        <v>1007593.884527753</v>
+        <v>8487.570829678751</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -21198,7 +21504,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Reactor Transport Cask Count</t>
+          <t>Production Rate</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -21223,11 +21529,11 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Roundtrip Time</t>
+          <t>Radioactive Waste Processing Hot Cell Count</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>0.01141552511415525</v>
+        <v>1</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -21248,11 +21554,11 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Roundtrip Time Reactor Transport</t>
+          <t>Radwaste Storage Warehouses Area</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>0.030441400304414</v>
+        <v>1007593.884527753</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -21273,11 +21579,11 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SER Account 30 to Account 20 Ratio</t>
+          <t>Reactor Transport Cask Count</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>0.5</v>
+        <v>100</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -21298,11 +21604,11 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>SER Account 716 to Accounts 711-715 Ratio</t>
+          <t>Roundtrip Time</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0.02</v>
+        <v>0.01141552511415525</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -21323,11 +21629,11 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SER Account 717 to Accounts 711-715 Ratio</t>
+          <t>Roundtrip Time Reactor Transport</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>0.075</v>
+        <v>0.030441400304414</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -21348,11 +21654,11 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>SER Account 741 to Account 20 Ratio</t>
+          <t>SER Account 30 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0.005</v>
+        <v>0.5</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -21373,11 +21679,11 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>SER Account 742 to Account 20 Ratio</t>
+          <t>SER Account 716 to Accounts 711-715 Ratio</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -21398,11 +21704,11 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>SER Account 743 to Account 20 Ratio</t>
+          <t>SER Account 717 to Accounts 711-715 Ratio</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>0.01</v>
+        <v>0.075</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -21423,11 +21729,11 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>SER Account 747.1 to Accounts 741-743 Ratio</t>
+          <t>SER Account 741 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>0.05</v>
+        <v>0.005</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -21448,11 +21754,11 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SER Account 747.4 to Account 20 Ratio</t>
+          <t>SER Account 742 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -21473,11 +21779,11 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SER Administration Building Area</t>
+          <t>SER Account 743 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>23969.5672563314</v>
+        <v>0.01</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -21498,11 +21804,11 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SER Campus Area</t>
+          <t>SER Account 747.1 to Accounts 741-743 Ratio</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>540.1637705987926</v>
+        <v>0.05</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -21523,11 +21829,11 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SER Campus Land Area</t>
+          <t>SER Account 747.4 to Account 20 Ratio</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>540.1637705987926</v>
+        <v>0.005</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -21548,11 +21854,11 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SER Construction Duration</t>
+          <t>SER Administration Building Area</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>36</v>
+        <v>23969.5672563314</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -21573,11 +21879,11 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SER Controlled Perimeter</t>
+          <t>SER Campus Area</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0</v>
+        <v>540.1637705987926</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -21598,11 +21904,11 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SER Emergency Generator Power</t>
+          <t>SER Campus Land Area</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>46.57835435991195</v>
+        <v>540.1637705987926</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -21623,11 +21929,11 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SER Engineering Headcount</t>
+          <t>SER Construction Duration</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>444</v>
+        <v>36</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -21648,11 +21954,11 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SER Fire Station Count</t>
+          <t>SER Controlled Perimeter</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -21673,11 +21979,11 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SER Guard Station Count</t>
+          <t>SER Emergency Generator Power</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>4</v>
+        <v>46.57835435991195</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -21698,11 +22004,11 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SER Helium Flowrate</t>
+          <t>SER Engineering Headcount</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>0.0006814490033629513</v>
+        <v>444</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -21723,11 +22029,11 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SER Local Control Building Area</t>
+          <t>SER Fire Station Count</t>
         </is>
       </c>
       <c r="C367" t="n">
-        <v>2680</v>
+        <v>3</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -21748,11 +22054,11 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SER Local Transport Vehicle Count</t>
+          <t>SER Guard Station Count</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -21773,11 +22079,11 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SER Maintenance Staff Per Shift</t>
+          <t>SER Helium Flowrate</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>1983</v>
+        <v>0.0006814490033629513</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -21798,11 +22104,11 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SER Motion Detector Count</t>
+          <t>SER Local Control Building Area</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>919</v>
+        <v>2680</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -21823,11 +22129,11 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SER Number of Operators Per Shift</t>
+          <t>SER Local Transport Vehicle Count</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -21848,11 +22154,11 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SER Protected Perimeter</t>
+          <t>SER Maintenance Staff Per Shift</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>1576.305198655893</v>
+        <v>1983</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -21873,11 +22179,11 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>SER Rad Waste Management Building Area</t>
+          <t>SER Motion Detector Count</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>927.5406006163373</v>
+        <v>919</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -21898,11 +22204,11 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>SER Radiation Monitor Count</t>
+          <t>SER Protected Perimeter</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>3</v>
+        <v>1576.305198655893</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -21923,11 +22229,11 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SER Remote Control Building Area</t>
+          <t>SER Rad Waste Management Building Area</t>
         </is>
       </c>
       <c r="C375" t="n">
-        <v>2680</v>
+        <v>927.5406006163373</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -21948,11 +22254,11 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SER Road Length</t>
+          <t>SER Radiation Monitor Count</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1775.790012416663</v>
+        <v>3</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -21973,11 +22279,11 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SER Security Building Area</t>
+          <t>SER Remote Control Building Area</t>
         </is>
       </c>
       <c r="C377" t="n">
-        <v>815.2440026135969</v>
+        <v>2680</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -21998,11 +22304,11 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SER Security Camera Count</t>
+          <t>SER Road Length</t>
         </is>
       </c>
       <c r="C378" t="n">
-        <v>579</v>
+        <v>1775.790012416663</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -22023,11 +22329,11 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SER Security Staff Per Shift</t>
+          <t>SER Security Building Area</t>
         </is>
       </c>
       <c r="C379" t="n">
-        <v>37</v>
+        <v>815.2440026135969</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -22048,11 +22354,11 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SER Site Perimeter</t>
+          <t>SER Security Camera Count</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1775.790012416663</v>
+        <v>579</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -22073,11 +22379,11 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SER Switchyard Average Power</t>
+          <t>SER Security Staff Per Shift</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>113.376424108743</v>
+        <v>37</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -22098,11 +22404,11 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SER Switchyard Rating</t>
+          <t>SER Site Perimeter</t>
         </is>
       </c>
       <c r="C382" t="n">
-        <v>226.7528482174859</v>
+        <v>1775.790012416663</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -22123,11 +22429,11 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SER Utility Vehicle Count</t>
+          <t>SER Switchyard Average Power</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>37</v>
+        <v>113.376424108743</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -22148,11 +22454,11 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Service Air Water Building Count</t>
+          <t>SER Switchyard Rating</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>226.7528482174859</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -22173,11 +22479,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Servicing Hot Cell Annual Rate</t>
+          <t>SER Utility Vehicle Count</t>
         </is>
       </c>
       <c r="C385" t="n">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -22198,11 +22504,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Servicing Hot Cell Building Area</t>
+          <t>Service Air Water Building Count</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>21600.15718003606</v>
+        <v>3</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -22223,11 +22529,11 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Servicing Rate</t>
+          <t>Servicing Hot Cell Annual Rate</t>
         </is>
       </c>
       <c r="C387" t="n">
-        <v>200.9911894273128</v>
+        <v>111</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -22248,11 +22554,11 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Servicing Total Time</t>
+          <t>Servicing Hot Cell Building Area</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>0.0273972602739726</v>
+        <v>21600.15718003606</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -22273,11 +22579,11 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Shift To Headcount</t>
+          <t>Servicing Rate</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>5</v>
+        <v>200.9911894273128</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -22298,11 +22604,11 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Used Fuel Storage Lifetime Capacity</t>
+          <t>Servicing Total Time</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>5632719.525310026</v>
+        <v>0.0273972602739726</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -22323,11 +22629,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Water Supply Frequency</t>
+          <t>Shift To Headcount</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -22348,11 +22654,11 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Water Tanker Truck Count</t>
+          <t>Used Fuel Storage Lifetime Capacity</t>
         </is>
       </c>
       <c r="C392" t="n">
-        <v>71</v>
+        <v>5632719.525310026</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -22373,24 +22679,74 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
+          <t>Water Supply Frequency</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>4</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Water Tanker Truck Count</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>71</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
           <t>m3_to_kg_He_RT_atmospheric</t>
         </is>
       </c>
-      <c r="C393" t="n">
+      <c r="C395" t="n">
         <v>0.1661</v>
       </c>
-      <c r="E393" t="inlineStr">
+      <c r="E395" t="inlineStr">
         <is>
           <t>--- Not in params registry. Please add to cost/params_registry.py ---</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr">
+      <c r="F395" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
     </row>
-    <row r="394"/>
+    <row r="396"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
